--- a/data/source/facilities-2026-04-30.xlsx
+++ b/data/source/facilities-2026-04-30.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JCR\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB57DC97-B198-48B3-BC13-FEF7FEF7FAFE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37EB5037-1007-4920-842E-B4B10B989C95}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8856" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4451" uniqueCount="1097">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4442" uniqueCount="1096">
   <si>
     <t>연번</t>
   </si>
@@ -1637,12 +1637,6 @@
   </si>
   <si>
     <t>경기 오산시 남부대로441번길 70-6</t>
-  </si>
-  <si>
-    <t>경기도 유도회관</t>
-  </si>
-  <si>
-    <t>경기 수원시 권선구 오목천동 서수원로63번길 127</t>
   </si>
   <si>
     <t>경기도 사격테마파크</t>
@@ -3314,6 +3308,10 @@
   </si>
   <si>
     <t>감면 내용</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -3609,6 +3607,36 @@
     <cellStyle name="하이퍼링크" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="20">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -3981,36 +4009,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -4025,21 +4023,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="예우시설목록" displayName="예우시설목록" ref="A1:L442" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:L442" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="예우시설목록" displayName="예우시설목록" ref="A1:L441" totalsRowShown="0" headerRowDxfId="19" dataDxfId="17" headerRowBorderDxfId="18" tableBorderDxfId="16" totalsRowBorderDxfId="15">
+  <autoFilter ref="A1:L441" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="연번" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="지역" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="업종" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="시설명" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="우대 대상" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="감면 내용" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="면제/할인" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="기관구분" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="비고" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="홈페이지 URL" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="주소" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="연락처" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="연번" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="지역" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="업종" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="시설명" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="우대 대상" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="감면 내용" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="면제/할인" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="기관구분" dataDxfId="7"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="비고" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="홈페이지 URL" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="주소" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="연락처" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4261,7 +4259,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L442"/>
+  <dimension ref="A1:L441"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.296875" customWidth="1"/>
@@ -4292,10 +4290,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>4</v>
@@ -5449,9 +5447,8 @@
       <c r="J31" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="K31" s="7" t="e">
-        <f>-K24</f>
-        <v>#VALUE!</v>
+      <c r="K31" s="7" t="s">
+        <v>1095</v>
       </c>
       <c r="L31" s="10" t="s">
         <v>32</v>
@@ -9312,7 +9309,7 @@
         <v>138</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="C139" s="7" t="s">
         <v>114</v>
@@ -9564,28 +9561,28 @@
         <v>145</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>536</v>
+        <v>318</v>
       </c>
       <c r="C146" s="7" t="s">
-        <v>75</v>
+        <v>231</v>
       </c>
       <c r="D146" s="7" t="s">
         <v>541</v>
       </c>
       <c r="E146" s="7" t="s">
-        <v>99</v>
+        <v>329</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>78</v>
+        <v>334</v>
       </c>
       <c r="G146" s="7" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H146" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I146" s="7" t="s">
-        <v>102</v>
+        <v>331</v>
       </c>
       <c r="J146" s="7" t="s">
         <v>32</v>
@@ -9612,10 +9609,10 @@
         <v>329</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>334</v>
+        <v>544</v>
       </c>
       <c r="G147" s="7" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H147" s="7" t="s">
         <v>16</v>
@@ -9627,7 +9624,7 @@
         <v>32</v>
       </c>
       <c r="K147" s="7" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="L147" s="10"/>
     </row>
@@ -9639,19 +9636,19 @@
         <v>318</v>
       </c>
       <c r="C148" s="7" t="s">
-        <v>231</v>
+        <v>11</v>
       </c>
       <c r="D148" s="7" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E148" s="7" t="s">
         <v>329</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>546</v>
+        <v>334</v>
       </c>
       <c r="G148" s="7" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H148" s="7" t="s">
         <v>16</v>
@@ -9756,10 +9753,10 @@
         <v>329</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>334</v>
+        <v>553</v>
       </c>
       <c r="G151" s="7" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H151" s="7" t="s">
         <v>16</v>
@@ -9771,7 +9768,7 @@
         <v>32</v>
       </c>
       <c r="K151" s="7" t="s">
-        <v>553</v>
+        <v>32</v>
       </c>
       <c r="L151" s="10"/>
     </row>
@@ -9780,31 +9777,31 @@
         <v>151</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>318</v>
+        <v>87</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="D152" s="7" t="s">
         <v>554</v>
       </c>
       <c r="E152" s="7" t="s">
-        <v>329</v>
+        <v>77</v>
       </c>
       <c r="F152" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G152" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H152" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I152" s="7" t="s">
         <v>555</v>
       </c>
-      <c r="G152" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H152" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I152" s="7" t="s">
-        <v>331</v>
-      </c>
       <c r="J152" s="7" t="s">
-        <v>32</v>
+        <v>556</v>
       </c>
       <c r="K152" s="7" t="s">
         <v>32</v>
@@ -9819,28 +9816,28 @@
         <v>87</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="D153" s="7" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E153" s="7" t="s">
         <v>77</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>14</v>
+        <v>558</v>
       </c>
       <c r="G153" s="7" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H153" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I153" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="J153" s="7" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="K153" s="7" t="s">
         <v>32</v>
@@ -9855,28 +9852,28 @@
         <v>87</v>
       </c>
       <c r="C154" s="7" t="s">
-        <v>114</v>
+        <v>26</v>
       </c>
       <c r="D154" s="7" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E154" s="7" t="s">
         <v>77</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="G154" s="7" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H154" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I154" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="J154" s="7" t="s">
-        <v>561</v>
+        <v>32</v>
       </c>
       <c r="K154" s="7" t="s">
         <v>32</v>
@@ -9900,19 +9897,19 @@
         <v>77</v>
       </c>
       <c r="F155" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G155" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H155" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I155" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="J155" s="7" t="s">
         <v>563</v>
-      </c>
-      <c r="G155" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H155" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I155" s="7" t="s">
-        <v>557</v>
-      </c>
-      <c r="J155" s="7" t="s">
-        <v>32</v>
       </c>
       <c r="K155" s="7" t="s">
         <v>32</v>
@@ -9927,7 +9924,7 @@
         <v>87</v>
       </c>
       <c r="C156" s="7" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="D156" s="7" t="s">
         <v>564</v>
@@ -9945,10 +9942,10 @@
         <v>16</v>
       </c>
       <c r="I156" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="J156" s="7" t="s">
-        <v>565</v>
+        <v>90</v>
       </c>
       <c r="K156" s="7" t="s">
         <v>32</v>
@@ -9963,10 +9960,10 @@
         <v>87</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="D157" s="7" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E157" s="7" t="s">
         <v>77</v>
@@ -9981,10 +9978,10 @@
         <v>16</v>
       </c>
       <c r="I157" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="J157" s="7" t="s">
-        <v>90</v>
+        <v>566</v>
       </c>
       <c r="K157" s="7" t="s">
         <v>32</v>
@@ -9999,7 +9996,7 @@
         <v>87</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>138</v>
+        <v>231</v>
       </c>
       <c r="D158" s="7" t="s">
         <v>567</v>
@@ -10008,22 +10005,22 @@
         <v>77</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>14</v>
+        <v>568</v>
       </c>
       <c r="G158" s="7" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H158" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I158" s="7" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="J158" s="7" t="s">
-        <v>568</v>
+        <v>32</v>
       </c>
       <c r="K158" s="7" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="L158" s="10"/>
     </row>
@@ -10032,34 +10029,34 @@
         <v>158</v>
       </c>
       <c r="B159" s="7" t="s">
-        <v>87</v>
+        <v>569</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>231</v>
+        <v>92</v>
       </c>
       <c r="D159" s="7" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E159" s="7" t="s">
-        <v>77</v>
+        <v>571</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>570</v>
+        <v>14</v>
       </c>
       <c r="G159" s="7" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H159" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I159" s="7" t="s">
-        <v>557</v>
+        <v>102</v>
       </c>
       <c r="J159" s="7" t="s">
-        <v>32</v>
+        <v>572</v>
       </c>
       <c r="K159" s="7" t="s">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="L159" s="10"/>
     </row>
@@ -10068,22 +10065,22 @@
         <v>159</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="D160" s="7" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E160" s="7" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>14</v>
+        <v>575</v>
       </c>
       <c r="G160" s="7" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H160" s="7" t="s">
         <v>16</v>
@@ -10092,10 +10089,10 @@
         <v>102</v>
       </c>
       <c r="J160" s="7" t="s">
-        <v>574</v>
+        <v>32</v>
       </c>
       <c r="K160" s="7" t="s">
-        <v>32</v>
+        <v>576</v>
       </c>
       <c r="L160" s="10"/>
     </row>
@@ -10104,19 +10101,19 @@
         <v>160</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C161" s="7" t="s">
         <v>114</v>
       </c>
       <c r="D161" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="E161" s="7" t="s">
+        <v>574</v>
+      </c>
+      <c r="F161" s="7" t="s">
         <v>575</v>
-      </c>
-      <c r="E161" s="7" t="s">
-        <v>576</v>
-      </c>
-      <c r="F161" s="7" t="s">
-        <v>577</v>
       </c>
       <c r="G161" s="7" t="s">
         <v>39</v>
@@ -10140,7 +10137,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C162" s="7" t="s">
         <v>114</v>
@@ -10149,10 +10146,10 @@
         <v>579</v>
       </c>
       <c r="E162" s="7" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="G162" s="7" t="s">
         <v>39</v>
@@ -10176,19 +10173,19 @@
         <v>162</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>114</v>
+        <v>26</v>
       </c>
       <c r="D163" s="7" t="s">
         <v>581</v>
       </c>
       <c r="E163" s="7" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="G163" s="7" t="s">
         <v>39</v>
@@ -10203,7 +10200,7 @@
         <v>32</v>
       </c>
       <c r="K163" s="7" t="s">
-        <v>582</v>
+        <v>32</v>
       </c>
       <c r="L163" s="10"/>
     </row>
@@ -10212,31 +10209,31 @@
         <v>163</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>571</v>
+        <v>216</v>
       </c>
       <c r="C164" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D164" s="7" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E164" s="7" t="s">
-        <v>584</v>
+        <v>159</v>
       </c>
       <c r="F164" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G164" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H164" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I164" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="J164" s="7" t="s">
         <v>585</v>
-      </c>
-      <c r="G164" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H164" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I164" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="J164" s="7" t="s">
-        <v>32</v>
       </c>
       <c r="K164" s="7" t="s">
         <v>32</v>
@@ -10248,19 +10245,19 @@
         <v>164</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>216</v>
+        <v>284</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D165" s="7" t="s">
         <v>586</v>
       </c>
       <c r="E165" s="7" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>14</v>
+        <v>587</v>
       </c>
       <c r="G165" s="7" t="s">
         <v>15</v>
@@ -10269,10 +10266,10 @@
         <v>16</v>
       </c>
       <c r="I165" s="7" t="s">
-        <v>218</v>
+        <v>588</v>
       </c>
       <c r="J165" s="7" t="s">
-        <v>587</v>
+        <v>292</v>
       </c>
       <c r="K165" s="7" t="s">
         <v>32</v>
@@ -10290,25 +10287,25 @@
         <v>11</v>
       </c>
       <c r="D166" s="7" t="s">
+        <v>589</v>
+      </c>
+      <c r="E166" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F166" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="G166" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H166" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I166" s="7" t="s">
         <v>588</v>
       </c>
-      <c r="E166" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F166" s="7" t="s">
-        <v>589</v>
-      </c>
-      <c r="G166" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H166" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I166" s="7" t="s">
-        <v>590</v>
-      </c>
       <c r="J166" s="7" t="s">
-        <v>292</v>
+        <v>32</v>
       </c>
       <c r="K166" s="7" t="s">
         <v>32</v>
@@ -10320,19 +10317,19 @@
         <v>166</v>
       </c>
       <c r="B167" s="7" t="s">
-        <v>284</v>
+        <v>216</v>
       </c>
       <c r="C167" s="7" t="s">
-        <v>11</v>
+        <v>231</v>
       </c>
       <c r="D167" s="7" t="s">
         <v>591</v>
       </c>
       <c r="E167" s="7" t="s">
-        <v>77</v>
+        <v>159</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>592</v>
+        <v>14</v>
       </c>
       <c r="G167" s="7" t="s">
         <v>15</v>
@@ -10341,7 +10338,7 @@
         <v>16</v>
       </c>
       <c r="I167" s="7" t="s">
-        <v>590</v>
+        <v>218</v>
       </c>
       <c r="J167" s="7" t="s">
         <v>32</v>
@@ -10356,19 +10353,19 @@
         <v>167</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>216</v>
+        <v>529</v>
       </c>
       <c r="C168" s="7" t="s">
-        <v>231</v>
+        <v>92</v>
       </c>
       <c r="D168" s="7" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E168" s="7" t="s">
         <v>159</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>14</v>
+        <v>593</v>
       </c>
       <c r="G168" s="7" t="s">
         <v>15</v>
@@ -10377,10 +10374,10 @@
         <v>16</v>
       </c>
       <c r="I168" s="7" t="s">
-        <v>218</v>
+        <v>594</v>
       </c>
       <c r="J168" s="7" t="s">
-        <v>32</v>
+        <v>595</v>
       </c>
       <c r="K168" s="7" t="s">
         <v>32</v>
@@ -10395,16 +10392,16 @@
         <v>529</v>
       </c>
       <c r="C169" s="7" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="D169" s="7" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="E169" s="7" t="s">
         <v>159</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="G169" s="7" t="s">
         <v>15</v>
@@ -10413,10 +10410,10 @@
         <v>16</v>
       </c>
       <c r="I169" s="7" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="J169" s="7" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="K169" s="7" t="s">
         <v>32</v>
@@ -10428,19 +10425,19 @@
         <v>169</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>529</v>
+        <v>599</v>
       </c>
       <c r="C170" s="7" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="D170" s="7" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="E170" s="7" t="s">
-        <v>159</v>
+        <v>601</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="G170" s="7" t="s">
         <v>15</v>
@@ -10449,13 +10446,13 @@
         <v>16</v>
       </c>
       <c r="I170" s="7" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="J170" s="7" t="s">
-        <v>600</v>
+        <v>32</v>
       </c>
       <c r="K170" s="7" t="s">
-        <v>32</v>
+        <v>604</v>
       </c>
       <c r="L170" s="10"/>
     </row>
@@ -10464,28 +10461,28 @@
         <v>170</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C171" s="7" t="s">
         <v>114</v>
       </c>
       <c r="D171" s="7" t="s">
+        <v>605</v>
+      </c>
+      <c r="E171" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="F171" s="7" t="s">
         <v>602</v>
       </c>
-      <c r="E171" s="7" t="s">
+      <c r="G171" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H171" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I171" s="7" t="s">
         <v>603</v>
-      </c>
-      <c r="F171" s="7" t="s">
-        <v>604</v>
-      </c>
-      <c r="G171" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H171" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I171" s="7" t="s">
-        <v>605</v>
       </c>
       <c r="J171" s="7" t="s">
         <v>32</v>
@@ -10500,34 +10497,34 @@
         <v>171</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C172" s="7" t="s">
-        <v>114</v>
+        <v>11</v>
       </c>
       <c r="D172" s="7" t="s">
         <v>607</v>
       </c>
       <c r="E172" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="F172" s="7" t="s">
+        <v>608</v>
+      </c>
+      <c r="G172" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H172" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I172" s="7" t="s">
         <v>603</v>
       </c>
-      <c r="F172" s="7" t="s">
-        <v>604</v>
-      </c>
-      <c r="G172" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H172" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I172" s="7" t="s">
-        <v>605</v>
-      </c>
       <c r="J172" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K172" s="7" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="L172" s="10"/>
     </row>
@@ -10536,34 +10533,34 @@
         <v>172</v>
       </c>
       <c r="B173" s="7" t="s">
+        <v>599</v>
+      </c>
+      <c r="C173" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D173" s="7" t="s">
+        <v>610</v>
+      </c>
+      <c r="E173" s="7" t="s">
         <v>601</v>
       </c>
-      <c r="C173" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D173" s="7" t="s">
-        <v>609</v>
-      </c>
-      <c r="E173" s="7" t="s">
+      <c r="F173" s="7" t="s">
+        <v>611</v>
+      </c>
+      <c r="G173" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H173" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I173" s="7" t="s">
         <v>603</v>
       </c>
-      <c r="F173" s="7" t="s">
-        <v>610</v>
-      </c>
-      <c r="G173" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H173" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I173" s="7" t="s">
-        <v>605</v>
-      </c>
       <c r="J173" s="7" t="s">
-        <v>32</v>
+        <v>612</v>
       </c>
       <c r="K173" s="7" t="s">
-        <v>611</v>
+        <v>32</v>
       </c>
       <c r="L173" s="10"/>
     </row>
@@ -10572,31 +10569,31 @@
         <v>173</v>
       </c>
       <c r="B174" s="7" t="s">
+        <v>599</v>
+      </c>
+      <c r="C174" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D174" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="E174" s="7" t="s">
         <v>601</v>
       </c>
-      <c r="C174" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D174" s="7" t="s">
-        <v>612</v>
-      </c>
-      <c r="E174" s="7" t="s">
+      <c r="F174" s="7" t="s">
+        <v>614</v>
+      </c>
+      <c r="G174" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H174" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I174" s="7" t="s">
         <v>603</v>
       </c>
-      <c r="F174" s="7" t="s">
-        <v>613</v>
-      </c>
-      <c r="G174" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H174" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I174" s="7" t="s">
-        <v>605</v>
-      </c>
       <c r="J174" s="7" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="K174" s="7" t="s">
         <v>32</v>
@@ -10608,34 +10605,34 @@
         <v>174</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C175" s="7" t="s">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="D175" s="7" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E175" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="F175" s="7" t="s">
+        <v>618</v>
+      </c>
+      <c r="G175" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H175" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I175" s="7" t="s">
         <v>603</v>
       </c>
-      <c r="F175" s="7" t="s">
-        <v>616</v>
-      </c>
-      <c r="G175" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H175" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I175" s="7" t="s">
-        <v>605</v>
-      </c>
       <c r="J175" s="7" t="s">
-        <v>617</v>
+        <v>32</v>
       </c>
       <c r="K175" s="7" t="s">
-        <v>32</v>
+        <v>619</v>
       </c>
       <c r="L175" s="10"/>
     </row>
@@ -10644,19 +10641,19 @@
         <v>175</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>601</v>
+        <v>476</v>
       </c>
       <c r="C176" s="7" t="s">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="D176" s="7" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="E176" s="7" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>620</v>
+        <v>39</v>
       </c>
       <c r="G176" s="7" t="s">
         <v>39</v>
@@ -10665,13 +10662,13 @@
         <v>16</v>
       </c>
       <c r="I176" s="7" t="s">
-        <v>605</v>
+        <v>622</v>
       </c>
       <c r="J176" s="7" t="s">
-        <v>32</v>
+        <v>623</v>
       </c>
       <c r="K176" s="7" t="s">
-        <v>621</v>
+        <v>32</v>
       </c>
       <c r="L176" s="10"/>
     </row>
@@ -10683,28 +10680,28 @@
         <v>476</v>
       </c>
       <c r="C177" s="7" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="D177" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="E177" s="7" t="s">
+        <v>621</v>
+      </c>
+      <c r="F177" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G177" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H177" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I177" s="7" t="s">
         <v>622</v>
       </c>
-      <c r="E177" s="7" t="s">
-        <v>623</v>
-      </c>
-      <c r="F177" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G177" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H177" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I177" s="7" t="s">
-        <v>624</v>
-      </c>
       <c r="J177" s="7" t="s">
-        <v>625</v>
+        <v>32</v>
       </c>
       <c r="K177" s="7" t="s">
         <v>32</v>
@@ -10716,16 +10713,16 @@
         <v>177</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>476</v>
+        <v>625</v>
       </c>
       <c r="C178" s="7" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="D178" s="7" t="s">
         <v>626</v>
       </c>
       <c r="E178" s="7" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="F178" s="7" t="s">
         <v>14</v>
@@ -10737,10 +10734,10 @@
         <v>16</v>
       </c>
       <c r="I178" s="7" t="s">
-        <v>624</v>
+        <v>102</v>
       </c>
       <c r="J178" s="7" t="s">
-        <v>32</v>
+        <v>628</v>
       </c>
       <c r="K178" s="7" t="s">
         <v>32</v>
@@ -10752,19 +10749,19 @@
         <v>178</v>
       </c>
       <c r="B179" s="7" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C179" s="7" t="s">
-        <v>114</v>
+        <v>11</v>
       </c>
       <c r="D179" s="7" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E179" s="7" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F179" s="7" t="s">
-        <v>14</v>
+        <v>631</v>
       </c>
       <c r="G179" s="7" t="s">
         <v>15</v>
@@ -10776,10 +10773,10 @@
         <v>102</v>
       </c>
       <c r="J179" s="7" t="s">
-        <v>630</v>
+        <v>32</v>
       </c>
       <c r="K179" s="7" t="s">
-        <v>32</v>
+        <v>632</v>
       </c>
       <c r="L179" s="10"/>
     </row>
@@ -10788,22 +10785,22 @@
         <v>179</v>
       </c>
       <c r="B180" s="7" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C180" s="7" t="s">
-        <v>11</v>
+        <v>138</v>
       </c>
       <c r="D180" s="7" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="E180" s="7" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="F180" s="7" t="s">
-        <v>633</v>
+        <v>334</v>
       </c>
       <c r="G180" s="7" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H180" s="7" t="s">
         <v>16</v>
@@ -10824,16 +10821,16 @@
         <v>180</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C181" s="7" t="s">
-        <v>138</v>
+        <v>11</v>
       </c>
       <c r="D181" s="7" t="s">
         <v>635</v>
       </c>
       <c r="E181" s="7" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="F181" s="7" t="s">
         <v>334</v>
@@ -10851,7 +10848,7 @@
         <v>32</v>
       </c>
       <c r="K181" s="7" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L181" s="10"/>
     </row>
@@ -10860,16 +10857,16 @@
         <v>181</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C182" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D182" s="7" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E182" s="7" t="s">
-        <v>638</v>
+        <v>478</v>
       </c>
       <c r="F182" s="7" t="s">
         <v>334</v>
@@ -10896,7 +10893,7 @@
         <v>182</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C183" s="7" t="s">
         <v>11</v>
@@ -10908,10 +10905,10 @@
         <v>478</v>
       </c>
       <c r="F183" s="7" t="s">
-        <v>334</v>
+        <v>641</v>
       </c>
       <c r="G183" s="7" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H183" s="7" t="s">
         <v>16</v>
@@ -10923,7 +10920,7 @@
         <v>32</v>
       </c>
       <c r="K183" s="7" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="L183" s="10"/>
     </row>
@@ -10932,19 +10929,19 @@
         <v>183</v>
       </c>
       <c r="B184" s="7" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C184" s="7" t="s">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="D184" s="7" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E184" s="7" t="s">
-        <v>478</v>
+        <v>644</v>
       </c>
       <c r="F184" s="7" t="s">
-        <v>643</v>
+        <v>330</v>
       </c>
       <c r="G184" s="7" t="s">
         <v>15</v>
@@ -10956,10 +10953,10 @@
         <v>102</v>
       </c>
       <c r="J184" s="7" t="s">
-        <v>32</v>
+        <v>645</v>
       </c>
       <c r="K184" s="7" t="s">
-        <v>644</v>
+        <v>32</v>
       </c>
       <c r="L184" s="10"/>
     </row>
@@ -10968,22 +10965,22 @@
         <v>184</v>
       </c>
       <c r="B185" s="7" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C185" s="7" t="s">
-        <v>92</v>
+        <v>26</v>
       </c>
       <c r="D185" s="7" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E185" s="7" t="s">
-        <v>646</v>
+        <v>478</v>
       </c>
       <c r="F185" s="7" t="s">
-        <v>330</v>
+        <v>647</v>
       </c>
       <c r="G185" s="7" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H185" s="7" t="s">
         <v>16</v>
@@ -10992,7 +10989,7 @@
         <v>102</v>
       </c>
       <c r="J185" s="7" t="s">
-        <v>647</v>
+        <v>32</v>
       </c>
       <c r="K185" s="7" t="s">
         <v>32</v>
@@ -11004,7 +11001,7 @@
         <v>185</v>
       </c>
       <c r="B186" s="7" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C186" s="7" t="s">
         <v>26</v>
@@ -11013,13 +11010,13 @@
         <v>648</v>
       </c>
       <c r="E186" s="7" t="s">
-        <v>478</v>
+        <v>649</v>
       </c>
       <c r="F186" s="7" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="G186" s="7" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H186" s="7" t="s">
         <v>16</v>
@@ -11040,19 +11037,19 @@
         <v>186</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C187" s="7" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="D187" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="E187" s="7" t="s">
+        <v>630</v>
+      </c>
+      <c r="F187" s="7" t="s">
         <v>650</v>
-      </c>
-      <c r="E187" s="7" t="s">
-        <v>651</v>
-      </c>
-      <c r="F187" s="7" t="s">
-        <v>652</v>
       </c>
       <c r="G187" s="7" t="s">
         <v>15</v>
@@ -11076,19 +11073,19 @@
         <v>187</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C188" s="7" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="D188" s="7" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E188" s="7" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="F188" s="7" t="s">
-        <v>652</v>
+        <v>544</v>
       </c>
       <c r="G188" s="7" t="s">
         <v>15</v>
@@ -11112,22 +11109,22 @@
         <v>188</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>627</v>
+        <v>515</v>
       </c>
       <c r="C189" s="7" t="s">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="D189" s="7" t="s">
+        <v>653</v>
+      </c>
+      <c r="E189" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="F189" s="7" t="s">
         <v>654</v>
       </c>
-      <c r="E189" s="7" t="s">
-        <v>632</v>
-      </c>
-      <c r="F189" s="7" t="s">
-        <v>546</v>
-      </c>
       <c r="G189" s="7" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H189" s="7" t="s">
         <v>16</v>
@@ -11148,7 +11145,7 @@
         <v>189</v>
       </c>
       <c r="B190" s="7" t="s">
-        <v>515</v>
+        <v>1092</v>
       </c>
       <c r="C190" s="7" t="s">
         <v>138</v>
@@ -11163,19 +11160,19 @@
         <v>656</v>
       </c>
       <c r="G190" s="7" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H190" s="7" t="s">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="I190" s="7" t="s">
-        <v>102</v>
+        <v>657</v>
       </c>
       <c r="J190" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K190" s="7" t="s">
-        <v>32</v>
+        <v>658</v>
       </c>
       <c r="L190" s="10"/>
     </row>
@@ -11184,34 +11181,34 @@
         <v>190</v>
       </c>
       <c r="B191" s="7" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="C191" s="7" t="s">
-        <v>138</v>
+        <v>26</v>
       </c>
       <c r="D191" s="7" t="s">
+        <v>659</v>
+      </c>
+      <c r="E191" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F191" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G191" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H191" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I191" s="7" t="s">
         <v>657</v>
       </c>
-      <c r="E191" s="7" t="s">
-        <v>478</v>
-      </c>
-      <c r="F191" s="7" t="s">
-        <v>658</v>
-      </c>
-      <c r="G191" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H191" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="I191" s="7" t="s">
-        <v>659</v>
-      </c>
       <c r="J191" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K191" s="7" t="s">
-        <v>660</v>
+        <v>32</v>
       </c>
       <c r="L191" s="10"/>
     </row>
@@ -11220,19 +11217,19 @@
         <v>191</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="C192" s="7" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="D192" s="7" t="s">
+        <v>660</v>
+      </c>
+      <c r="E192" s="7" t="s">
         <v>661</v>
       </c>
-      <c r="E192" s="7" t="s">
-        <v>13</v>
-      </c>
       <c r="F192" s="7" t="s">
-        <v>14</v>
+        <v>662</v>
       </c>
       <c r="G192" s="7" t="s">
         <v>15</v>
@@ -11241,13 +11238,13 @@
         <v>16</v>
       </c>
       <c r="I192" s="7" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="J192" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K192" s="7" t="s">
-        <v>32</v>
+        <v>663</v>
       </c>
       <c r="L192" s="10"/>
     </row>
@@ -11256,34 +11253,34 @@
         <v>192</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="C193" s="7" t="s">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="D193" s="7" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="E193" s="7" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="F193" s="7" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="G193" s="7" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H193" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I193" s="7" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="J193" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K193" s="7" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="L193" s="10"/>
     </row>
@@ -11292,34 +11289,34 @@
         <v>193</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="C194" s="7" t="s">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="D194" s="7" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E194" s="7" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="F194" s="7" t="s">
-        <v>668</v>
+        <v>14</v>
       </c>
       <c r="G194" s="7" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H194" s="7" t="s">
-        <v>16</v>
+        <v>670</v>
       </c>
       <c r="I194" s="7" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="J194" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K194" s="7" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="L194" s="10"/>
     </row>
@@ -11328,16 +11325,16 @@
         <v>194</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>1094</v>
+        <v>672</v>
       </c>
       <c r="C195" s="7" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="D195" s="7" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="E195" s="7" t="s">
-        <v>671</v>
+        <v>478</v>
       </c>
       <c r="F195" s="7" t="s">
         <v>14</v>
@@ -11346,16 +11343,16 @@
         <v>15</v>
       </c>
       <c r="H195" s="7" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="I195" s="7" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="J195" s="7" t="s">
-        <v>32</v>
+        <v>674</v>
       </c>
       <c r="K195" s="7" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="L195" s="10"/>
     </row>
@@ -11364,34 +11361,34 @@
         <v>195</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>674</v>
+        <v>518</v>
       </c>
       <c r="C196" s="7" t="s">
-        <v>92</v>
+        <v>138</v>
       </c>
       <c r="D196" s="7" t="s">
         <v>675</v>
       </c>
       <c r="E196" s="7" t="s">
-        <v>478</v>
+        <v>675</v>
       </c>
       <c r="F196" s="7" t="s">
-        <v>14</v>
+        <v>553</v>
       </c>
       <c r="G196" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H196" s="7" t="s">
-        <v>672</v>
+        <v>16</v>
       </c>
       <c r="I196" s="7" t="s">
-        <v>659</v>
+        <v>676</v>
       </c>
       <c r="J196" s="7" t="s">
-        <v>676</v>
+        <v>32</v>
       </c>
       <c r="K196" s="7" t="s">
-        <v>673</v>
+        <v>32</v>
       </c>
       <c r="L196" s="10"/>
     </row>
@@ -11403,31 +11400,31 @@
         <v>518</v>
       </c>
       <c r="C197" s="7" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="D197" s="7" t="s">
         <v>677</v>
       </c>
       <c r="E197" s="7" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F197" s="7" t="s">
-        <v>555</v>
+        <v>39</v>
       </c>
       <c r="G197" s="7" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H197" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I197" s="7" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="J197" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K197" s="7" t="s">
-        <v>32</v>
+        <v>679</v>
       </c>
       <c r="L197" s="10"/>
     </row>
@@ -11439,31 +11436,31 @@
         <v>518</v>
       </c>
       <c r="C198" s="7" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="D198" s="7" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="E198" s="7" t="s">
         <v>680</v>
       </c>
       <c r="F198" s="7" t="s">
-        <v>39</v>
+        <v>681</v>
       </c>
       <c r="G198" s="7" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H198" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I198" s="7" t="s">
-        <v>678</v>
-      </c>
-      <c r="J198" s="7" t="s">
-        <v>32</v>
+        <v>676</v>
+      </c>
+      <c r="J198" s="8" t="s">
+        <v>682</v>
       </c>
       <c r="K198" s="7" t="s">
-        <v>681</v>
+        <v>32</v>
       </c>
       <c r="L198" s="10"/>
     </row>
@@ -11475,16 +11472,16 @@
         <v>518</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="D199" s="7" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E199" s="7" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="F199" s="7" t="s">
-        <v>683</v>
+        <v>14</v>
       </c>
       <c r="G199" s="7" t="s">
         <v>15</v>
@@ -11493,13 +11490,13 @@
         <v>16</v>
       </c>
       <c r="I199" s="7" t="s">
-        <v>678</v>
-      </c>
-      <c r="J199" s="8" t="s">
-        <v>684</v>
+        <v>676</v>
+      </c>
+      <c r="J199" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="K199" s="7" t="s">
-        <v>32</v>
+        <v>685</v>
       </c>
       <c r="L199" s="10"/>
     </row>
@@ -11514,10 +11511,10 @@
         <v>75</v>
       </c>
       <c r="D200" s="7" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E200" s="7" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F200" s="7" t="s">
         <v>14</v>
@@ -11529,7 +11526,7 @@
         <v>16</v>
       </c>
       <c r="I200" s="7" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="J200" s="7" t="s">
         <v>32</v>
@@ -11553,7 +11550,7 @@
         <v>688</v>
       </c>
       <c r="E201" s="7" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F201" s="7" t="s">
         <v>14</v>
@@ -11565,7 +11562,7 @@
         <v>16</v>
       </c>
       <c r="I201" s="7" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="J201" s="7" t="s">
         <v>32</v>
@@ -11589,7 +11586,7 @@
         <v>690</v>
       </c>
       <c r="E202" s="7" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F202" s="7" t="s">
         <v>14</v>
@@ -11601,7 +11598,7 @@
         <v>16</v>
       </c>
       <c r="I202" s="7" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="J202" s="7" t="s">
         <v>32</v>
@@ -11625,7 +11622,7 @@
         <v>692</v>
       </c>
       <c r="E203" s="7" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F203" s="7" t="s">
         <v>14</v>
@@ -11637,7 +11634,7 @@
         <v>16</v>
       </c>
       <c r="I203" s="7" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="J203" s="7" t="s">
         <v>32</v>
@@ -11661,7 +11658,7 @@
         <v>694</v>
       </c>
       <c r="E204" s="7" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F204" s="7" t="s">
         <v>14</v>
@@ -11673,7 +11670,7 @@
         <v>16</v>
       </c>
       <c r="I204" s="7" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="J204" s="7" t="s">
         <v>32</v>
@@ -11697,7 +11694,7 @@
         <v>696</v>
       </c>
       <c r="E205" s="7" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F205" s="7" t="s">
         <v>14</v>
@@ -11709,13 +11706,13 @@
         <v>16</v>
       </c>
       <c r="I205" s="7" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="J205" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K205" s="7" t="s">
-        <v>697</v>
+        <v>32</v>
       </c>
       <c r="L205" s="10"/>
     </row>
@@ -11730,10 +11727,10 @@
         <v>75</v>
       </c>
       <c r="D206" s="7" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E206" s="7" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F206" s="7" t="s">
         <v>14</v>
@@ -11745,13 +11742,13 @@
         <v>16</v>
       </c>
       <c r="I206" s="7" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="J206" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K206" s="7" t="s">
-        <v>32</v>
+        <v>698</v>
       </c>
       <c r="L206" s="10"/>
     </row>
@@ -11769,7 +11766,7 @@
         <v>699</v>
       </c>
       <c r="E207" s="7" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F207" s="7" t="s">
         <v>14</v>
@@ -11781,13 +11778,13 @@
         <v>16</v>
       </c>
       <c r="I207" s="7" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="J207" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K207" s="7" t="s">
-        <v>700</v>
+        <v>32</v>
       </c>
       <c r="L207" s="10"/>
     </row>
@@ -11802,10 +11799,10 @@
         <v>75</v>
       </c>
       <c r="D208" s="7" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="E208" s="7" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F208" s="7" t="s">
         <v>14</v>
@@ -11817,13 +11814,13 @@
         <v>16</v>
       </c>
       <c r="I208" s="7" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="J208" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K208" s="7" t="s">
-        <v>32</v>
+        <v>701</v>
       </c>
       <c r="L208" s="10"/>
     </row>
@@ -11841,7 +11838,7 @@
         <v>702</v>
       </c>
       <c r="E209" s="7" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F209" s="7" t="s">
         <v>14</v>
@@ -11853,7 +11850,7 @@
         <v>16</v>
       </c>
       <c r="I209" s="7" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="J209" s="7" t="s">
         <v>32</v>
@@ -11877,7 +11874,7 @@
         <v>704</v>
       </c>
       <c r="E210" s="7" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F210" s="7" t="s">
         <v>14</v>
@@ -11889,13 +11886,13 @@
         <v>16</v>
       </c>
       <c r="I210" s="7" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="J210" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K210" s="7" t="s">
-        <v>705</v>
+        <v>32</v>
       </c>
       <c r="L210" s="10"/>
     </row>
@@ -11910,10 +11907,10 @@
         <v>75</v>
       </c>
       <c r="D211" s="7" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E211" s="7" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F211" s="7" t="s">
         <v>14</v>
@@ -11925,13 +11922,13 @@
         <v>16</v>
       </c>
       <c r="I211" s="7" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="J211" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K211" s="7" t="s">
-        <v>32</v>
+        <v>706</v>
       </c>
       <c r="L211" s="10"/>
     </row>
@@ -11949,7 +11946,7 @@
         <v>707</v>
       </c>
       <c r="E212" s="7" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F212" s="7" t="s">
         <v>14</v>
@@ -11961,7 +11958,7 @@
         <v>16</v>
       </c>
       <c r="I212" s="7" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="J212" s="7" t="s">
         <v>32</v>
@@ -11985,7 +11982,7 @@
         <v>709</v>
       </c>
       <c r="E213" s="7" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F213" s="7" t="s">
         <v>14</v>
@@ -11997,7 +11994,7 @@
         <v>16</v>
       </c>
       <c r="I213" s="7" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="J213" s="7" t="s">
         <v>32</v>
@@ -12021,7 +12018,7 @@
         <v>711</v>
       </c>
       <c r="E214" s="7" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F214" s="7" t="s">
         <v>14</v>
@@ -12033,7 +12030,7 @@
         <v>16</v>
       </c>
       <c r="I214" s="7" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="J214" s="7" t="s">
         <v>32</v>
@@ -12057,7 +12054,7 @@
         <v>713</v>
       </c>
       <c r="E215" s="7" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F215" s="7" t="s">
         <v>14</v>
@@ -12069,7 +12066,7 @@
         <v>16</v>
       </c>
       <c r="I215" s="7" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="J215" s="7" t="s">
         <v>32</v>
@@ -12084,16 +12081,16 @@
         <v>215</v>
       </c>
       <c r="B216" s="7" t="s">
-        <v>518</v>
+        <v>224</v>
       </c>
       <c r="C216" s="7" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="D216" s="7" t="s">
         <v>715</v>
       </c>
       <c r="E216" s="7" t="s">
-        <v>686</v>
+        <v>716</v>
       </c>
       <c r="F216" s="7" t="s">
         <v>14</v>
@@ -12105,13 +12102,13 @@
         <v>16</v>
       </c>
       <c r="I216" s="7" t="s">
-        <v>678</v>
+        <v>717</v>
       </c>
       <c r="J216" s="7" t="s">
-        <v>32</v>
+        <v>227</v>
       </c>
       <c r="K216" s="7" t="s">
-        <v>716</v>
+        <v>32</v>
       </c>
       <c r="L216" s="10"/>
     </row>
@@ -12126,10 +12123,10 @@
         <v>92</v>
       </c>
       <c r="D217" s="7" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="E217" s="7" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="F217" s="7" t="s">
         <v>14</v>
@@ -12141,10 +12138,10 @@
         <v>16</v>
       </c>
       <c r="I217" s="7" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="J217" s="7" t="s">
-        <v>227</v>
+        <v>32</v>
       </c>
       <c r="K217" s="7" t="s">
         <v>32</v>
@@ -12159,13 +12156,13 @@
         <v>224</v>
       </c>
       <c r="C218" s="7" t="s">
-        <v>92</v>
+        <v>26</v>
       </c>
       <c r="D218" s="7" t="s">
+        <v>719</v>
+      </c>
+      <c r="E218" s="7" t="s">
         <v>720</v>
-      </c>
-      <c r="E218" s="7" t="s">
-        <v>718</v>
       </c>
       <c r="F218" s="7" t="s">
         <v>14</v>
@@ -12177,7 +12174,7 @@
         <v>16</v>
       </c>
       <c r="I218" s="7" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="J218" s="7" t="s">
         <v>32</v>
@@ -12195,13 +12192,13 @@
         <v>224</v>
       </c>
       <c r="C219" s="7" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="D219" s="7" t="s">
         <v>721</v>
       </c>
       <c r="E219" s="7" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="F219" s="7" t="s">
         <v>14</v>
@@ -12213,7 +12210,7 @@
         <v>16</v>
       </c>
       <c r="I219" s="7" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="J219" s="7" t="s">
         <v>32</v>
@@ -12228,34 +12225,34 @@
         <v>219</v>
       </c>
       <c r="B220" s="7" t="s">
-        <v>224</v>
+        <v>722</v>
       </c>
       <c r="C220" s="7" t="s">
-        <v>75</v>
+        <v>231</v>
       </c>
       <c r="D220" s="7" t="s">
         <v>723</v>
       </c>
       <c r="E220" s="7" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="F220" s="7" t="s">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="G220" s="7" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H220" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I220" s="7" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="J220" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K220" s="7" t="s">
-        <v>32</v>
+        <v>726</v>
       </c>
       <c r="L220" s="10"/>
     </row>
@@ -12264,19 +12261,19 @@
         <v>220</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C221" s="7" t="s">
-        <v>231</v>
+        <v>138</v>
       </c>
       <c r="D221" s="7" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="E221" s="7" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="F221" s="7" t="s">
-        <v>100</v>
+        <v>729</v>
       </c>
       <c r="G221" s="7" t="s">
         <v>39</v>
@@ -12285,13 +12282,13 @@
         <v>16</v>
       </c>
       <c r="I221" s="7" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="J221" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K221" s="7" t="s">
-        <v>728</v>
+        <v>32</v>
       </c>
       <c r="L221" s="10"/>
     </row>
@@ -12300,34 +12297,34 @@
         <v>221</v>
       </c>
       <c r="B222" s="7" t="s">
+        <v>722</v>
+      </c>
+      <c r="C222" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D222" s="7" t="s">
+        <v>730</v>
+      </c>
+      <c r="E222" s="7" t="s">
         <v>724</v>
-      </c>
-      <c r="C222" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="D222" s="7" t="s">
-        <v>729</v>
-      </c>
-      <c r="E222" s="7" t="s">
-        <v>730</v>
       </c>
       <c r="F222" s="7" t="s">
         <v>731</v>
       </c>
       <c r="G222" s="7" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H222" s="7" t="s">
-        <v>16</v>
+        <v>117</v>
       </c>
       <c r="I222" s="7" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="J222" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K222" s="7" t="s">
-        <v>32</v>
+        <v>732</v>
       </c>
       <c r="L222" s="10"/>
     </row>
@@ -12336,34 +12333,34 @@
         <v>222</v>
       </c>
       <c r="B223" s="7" t="s">
-        <v>724</v>
+        <v>241</v>
       </c>
       <c r="C223" s="7" t="s">
         <v>114</v>
       </c>
       <c r="D223" s="7" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="E223" s="7" t="s">
-        <v>726</v>
+        <v>243</v>
       </c>
       <c r="F223" s="7" t="s">
-        <v>733</v>
+        <v>155</v>
       </c>
       <c r="G223" s="7" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H223" s="7" t="s">
-        <v>117</v>
+        <v>16</v>
       </c>
       <c r="I223" s="7" t="s">
-        <v>727</v>
+        <v>244</v>
       </c>
       <c r="J223" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K223" s="7" t="s">
-        <v>734</v>
+        <v>248</v>
       </c>
       <c r="L223" s="10"/>
     </row>
@@ -12375,19 +12372,19 @@
         <v>241</v>
       </c>
       <c r="C224" s="7" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="D224" s="7" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E224" s="7" t="s">
         <v>243</v>
       </c>
       <c r="F224" s="7" t="s">
-        <v>155</v>
+        <v>78</v>
       </c>
       <c r="G224" s="7" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H224" s="7" t="s">
         <v>16</v>
@@ -12399,7 +12396,7 @@
         <v>32</v>
       </c>
       <c r="K224" s="7" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="L224" s="10"/>
     </row>
@@ -12411,16 +12408,16 @@
         <v>241</v>
       </c>
       <c r="C225" s="7" t="s">
-        <v>138</v>
+        <v>92</v>
       </c>
       <c r="D225" s="7" t="s">
+        <v>735</v>
+      </c>
+      <c r="E225" s="7" t="s">
         <v>736</v>
       </c>
-      <c r="E225" s="7" t="s">
-        <v>243</v>
-      </c>
       <c r="F225" s="7" t="s">
-        <v>78</v>
+        <v>737</v>
       </c>
       <c r="G225" s="7" t="s">
         <v>15</v>
@@ -12432,10 +12429,10 @@
         <v>244</v>
       </c>
       <c r="J225" s="7" t="s">
-        <v>32</v>
+        <v>738</v>
       </c>
       <c r="K225" s="7" t="s">
-        <v>257</v>
+        <v>32</v>
       </c>
       <c r="L225" s="10"/>
     </row>
@@ -12447,16 +12444,16 @@
         <v>241</v>
       </c>
       <c r="C226" s="7" t="s">
-        <v>92</v>
+        <v>138</v>
       </c>
       <c r="D226" s="7" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="E226" s="7" t="s">
-        <v>738</v>
+        <v>243</v>
       </c>
       <c r="F226" s="7" t="s">
-        <v>739</v>
+        <v>78</v>
       </c>
       <c r="G226" s="7" t="s">
         <v>15</v>
@@ -12468,7 +12465,7 @@
         <v>244</v>
       </c>
       <c r="J226" s="7" t="s">
-        <v>740</v>
+        <v>32</v>
       </c>
       <c r="K226" s="7" t="s">
         <v>32</v>
@@ -12480,19 +12477,19 @@
         <v>226</v>
       </c>
       <c r="B227" s="7" t="s">
-        <v>241</v>
+        <v>740</v>
       </c>
       <c r="C227" s="7" t="s">
-        <v>138</v>
+        <v>26</v>
       </c>
       <c r="D227" s="7" t="s">
         <v>741</v>
       </c>
       <c r="E227" s="7" t="s">
-        <v>243</v>
+        <v>742</v>
       </c>
       <c r="F227" s="7" t="s">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="G227" s="7" t="s">
         <v>15</v>
@@ -12501,7 +12498,7 @@
         <v>16</v>
       </c>
       <c r="I227" s="7" t="s">
-        <v>244</v>
+        <v>743</v>
       </c>
       <c r="J227" s="7" t="s">
         <v>32</v>
@@ -12516,16 +12513,16 @@
         <v>227</v>
       </c>
       <c r="B228" s="7" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C228" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D228" s="7" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="E228" s="7" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="F228" s="7" t="s">
         <v>172</v>
@@ -12537,7 +12534,7 @@
         <v>16</v>
       </c>
       <c r="I228" s="7" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="J228" s="7" t="s">
         <v>32</v>
@@ -12552,16 +12549,16 @@
         <v>228</v>
       </c>
       <c r="B229" s="7" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C229" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D229" s="7" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="E229" s="7" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="F229" s="7" t="s">
         <v>172</v>
@@ -12573,7 +12570,7 @@
         <v>16</v>
       </c>
       <c r="I229" s="7" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="J229" s="7" t="s">
         <v>32</v>
@@ -12588,16 +12585,16 @@
         <v>229</v>
       </c>
       <c r="B230" s="7" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C230" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D230" s="7" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="E230" s="7" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="F230" s="7" t="s">
         <v>172</v>
@@ -12609,7 +12606,7 @@
         <v>16</v>
       </c>
       <c r="I230" s="7" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="J230" s="7" t="s">
         <v>32</v>
@@ -12624,16 +12621,16 @@
         <v>230</v>
       </c>
       <c r="B231" s="7" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C231" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D231" s="7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E231" s="7" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="F231" s="7" t="s">
         <v>172</v>
@@ -12645,7 +12642,7 @@
         <v>16</v>
       </c>
       <c r="I231" s="7" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="J231" s="7" t="s">
         <v>32</v>
@@ -12660,19 +12657,19 @@
         <v>231</v>
       </c>
       <c r="B232" s="7" t="s">
-        <v>742</v>
+        <v>508</v>
       </c>
       <c r="C232" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D232" s="7" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E232" s="7" t="s">
-        <v>744</v>
+        <v>478</v>
       </c>
       <c r="F232" s="7" t="s">
-        <v>172</v>
+        <v>14</v>
       </c>
       <c r="G232" s="7" t="s">
         <v>15</v>
@@ -12681,7 +12678,7 @@
         <v>16</v>
       </c>
       <c r="I232" s="7" t="s">
-        <v>745</v>
+        <v>102</v>
       </c>
       <c r="J232" s="7" t="s">
         <v>32</v>
@@ -12702,7 +12699,7 @@
         <v>26</v>
       </c>
       <c r="D233" s="7" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="E233" s="7" t="s">
         <v>478</v>
@@ -12720,7 +12717,7 @@
         <v>102</v>
       </c>
       <c r="J233" s="7" t="s">
-        <v>32</v>
+        <v>750</v>
       </c>
       <c r="K233" s="7" t="s">
         <v>32</v>
@@ -12741,7 +12738,7 @@
         <v>751</v>
       </c>
       <c r="E234" s="7" t="s">
-        <v>478</v>
+        <v>752</v>
       </c>
       <c r="F234" s="7" t="s">
         <v>14</v>
@@ -12756,7 +12753,7 @@
         <v>102</v>
       </c>
       <c r="J234" s="7" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="K234" s="7" t="s">
         <v>32</v>
@@ -12774,13 +12771,13 @@
         <v>26</v>
       </c>
       <c r="D235" s="7" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E235" s="7" t="s">
-        <v>754</v>
+        <v>478</v>
       </c>
       <c r="F235" s="7" t="s">
-        <v>14</v>
+        <v>172</v>
       </c>
       <c r="G235" s="7" t="s">
         <v>15</v>
@@ -12792,7 +12789,7 @@
         <v>102</v>
       </c>
       <c r="J235" s="7" t="s">
-        <v>755</v>
+        <v>32</v>
       </c>
       <c r="K235" s="7" t="s">
         <v>32</v>
@@ -12810,13 +12807,13 @@
         <v>26</v>
       </c>
       <c r="D236" s="7" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E236" s="7" t="s">
         <v>478</v>
       </c>
       <c r="F236" s="7" t="s">
-        <v>172</v>
+        <v>14</v>
       </c>
       <c r="G236" s="7" t="s">
         <v>15</v>
@@ -12831,7 +12828,7 @@
         <v>32</v>
       </c>
       <c r="K236" s="7" t="s">
-        <v>32</v>
+        <v>756</v>
       </c>
       <c r="L236" s="10"/>
     </row>
@@ -12849,10 +12846,10 @@
         <v>757</v>
       </c>
       <c r="E237" s="7" t="s">
-        <v>478</v>
+        <v>752</v>
       </c>
       <c r="F237" s="7" t="s">
-        <v>14</v>
+        <v>172</v>
       </c>
       <c r="G237" s="7" t="s">
         <v>15</v>
@@ -12885,13 +12882,13 @@
         <v>759</v>
       </c>
       <c r="E238" s="7" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="F238" s="7" t="s">
-        <v>172</v>
+        <v>334</v>
       </c>
       <c r="G238" s="7" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H238" s="7" t="s">
         <v>16</v>
@@ -12921,10 +12918,10 @@
         <v>761</v>
       </c>
       <c r="E239" s="7" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="F239" s="7" t="s">
-        <v>334</v>
+        <v>762</v>
       </c>
       <c r="G239" s="7" t="s">
         <v>39</v>
@@ -12939,7 +12936,7 @@
         <v>32</v>
       </c>
       <c r="K239" s="7" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="L239" s="10"/>
     </row>
@@ -12954,16 +12951,16 @@
         <v>26</v>
       </c>
       <c r="D240" s="7" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="E240" s="7" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="F240" s="7" t="s">
-        <v>764</v>
+        <v>14</v>
       </c>
       <c r="G240" s="7" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H240" s="7" t="s">
         <v>16</v>
@@ -12984,19 +12981,19 @@
         <v>240</v>
       </c>
       <c r="B241" s="7" t="s">
-        <v>508</v>
+        <v>170</v>
       </c>
       <c r="C241" s="7" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="D241" s="7" t="s">
         <v>766</v>
       </c>
       <c r="E241" s="7" t="s">
-        <v>754</v>
+        <v>13</v>
       </c>
       <c r="F241" s="7" t="s">
-        <v>14</v>
+        <v>172</v>
       </c>
       <c r="G241" s="7" t="s">
         <v>15</v>
@@ -13005,13 +13002,13 @@
         <v>16</v>
       </c>
       <c r="I241" s="7" t="s">
-        <v>102</v>
+        <v>767</v>
       </c>
       <c r="J241" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K241" s="7" t="s">
-        <v>767</v>
+        <v>32</v>
       </c>
       <c r="L241" s="10"/>
     </row>
@@ -13023,16 +13020,16 @@
         <v>170</v>
       </c>
       <c r="C242" s="7" t="s">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="D242" s="7" t="s">
         <v>768</v>
       </c>
       <c r="E242" s="7" t="s">
-        <v>13</v>
+        <v>769</v>
       </c>
       <c r="F242" s="7" t="s">
-        <v>172</v>
+        <v>14</v>
       </c>
       <c r="G242" s="7" t="s">
         <v>15</v>
@@ -13041,7 +13038,7 @@
         <v>16</v>
       </c>
       <c r="I242" s="7" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="J242" s="7" t="s">
         <v>32</v>
@@ -13056,16 +13053,16 @@
         <v>242</v>
       </c>
       <c r="B243" s="7" t="s">
-        <v>170</v>
+        <v>453</v>
       </c>
       <c r="C243" s="7" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="D243" s="7" t="s">
         <v>770</v>
       </c>
       <c r="E243" s="7" t="s">
-        <v>771</v>
+        <v>77</v>
       </c>
       <c r="F243" s="7" t="s">
         <v>14</v>
@@ -13077,13 +13074,13 @@
         <v>16</v>
       </c>
       <c r="I243" s="7" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="J243" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K243" s="7" t="s">
-        <v>32</v>
+        <v>772</v>
       </c>
       <c r="L243" s="10"/>
     </row>
@@ -13098,7 +13095,7 @@
         <v>92</v>
       </c>
       <c r="D244" s="7" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="E244" s="7" t="s">
         <v>77</v>
@@ -13113,7 +13110,7 @@
         <v>16</v>
       </c>
       <c r="I244" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J244" s="7" t="s">
         <v>32</v>
@@ -13149,7 +13146,7 @@
         <v>16</v>
       </c>
       <c r="I245" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J245" s="7" t="s">
         <v>32</v>
@@ -13185,7 +13182,7 @@
         <v>16</v>
       </c>
       <c r="I246" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J246" s="7" t="s">
         <v>32</v>
@@ -13221,13 +13218,13 @@
         <v>16</v>
       </c>
       <c r="I247" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J247" s="7" t="s">
-        <v>32</v>
+        <v>459</v>
       </c>
       <c r="K247" s="7" t="s">
-        <v>780</v>
+        <v>32</v>
       </c>
       <c r="L247" s="10"/>
     </row>
@@ -13242,7 +13239,7 @@
         <v>92</v>
       </c>
       <c r="D248" s="7" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="E248" s="7" t="s">
         <v>77</v>
@@ -13257,7 +13254,7 @@
         <v>16</v>
       </c>
       <c r="I248" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J248" s="7" t="s">
         <v>459</v>
@@ -13278,7 +13275,7 @@
         <v>92</v>
       </c>
       <c r="D249" s="7" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="E249" s="7" t="s">
         <v>77</v>
@@ -13293,13 +13290,13 @@
         <v>16</v>
       </c>
       <c r="I249" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J249" s="7" t="s">
-        <v>459</v>
+        <v>32</v>
       </c>
       <c r="K249" s="7" t="s">
-        <v>32</v>
+        <v>782</v>
       </c>
       <c r="L249" s="10"/>
     </row>
@@ -13329,7 +13326,7 @@
         <v>16</v>
       </c>
       <c r="I250" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J250" s="7" t="s">
         <v>32</v>
@@ -13365,7 +13362,7 @@
         <v>16</v>
       </c>
       <c r="I251" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J251" s="7" t="s">
         <v>32</v>
@@ -13401,7 +13398,7 @@
         <v>16</v>
       </c>
       <c r="I252" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J252" s="7" t="s">
         <v>32</v>
@@ -13437,13 +13434,13 @@
         <v>16</v>
       </c>
       <c r="I253" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J253" s="7" t="s">
-        <v>32</v>
+        <v>459</v>
       </c>
       <c r="K253" s="7" t="s">
-        <v>790</v>
+        <v>32</v>
       </c>
       <c r="L253" s="10"/>
     </row>
@@ -13458,7 +13455,7 @@
         <v>92</v>
       </c>
       <c r="D254" s="7" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E254" s="7" t="s">
         <v>77</v>
@@ -13473,13 +13470,13 @@
         <v>16</v>
       </c>
       <c r="I254" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J254" s="7" t="s">
-        <v>459</v>
+        <v>32</v>
       </c>
       <c r="K254" s="7" t="s">
-        <v>32</v>
+        <v>791</v>
       </c>
       <c r="L254" s="10"/>
     </row>
@@ -13509,13 +13506,13 @@
         <v>16</v>
       </c>
       <c r="I255" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J255" s="7" t="s">
-        <v>32</v>
+        <v>459</v>
       </c>
       <c r="K255" s="7" t="s">
-        <v>793</v>
+        <v>32</v>
       </c>
       <c r="L255" s="10"/>
     </row>
@@ -13530,7 +13527,7 @@
         <v>92</v>
       </c>
       <c r="D256" s="7" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E256" s="7" t="s">
         <v>77</v>
@@ -13545,7 +13542,7 @@
         <v>16</v>
       </c>
       <c r="I256" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J256" s="7" t="s">
         <v>459</v>
@@ -13566,7 +13563,7 @@
         <v>92</v>
       </c>
       <c r="D257" s="7" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="E257" s="7" t="s">
         <v>77</v>
@@ -13581,7 +13578,7 @@
         <v>16</v>
       </c>
       <c r="I257" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J257" s="7" t="s">
         <v>459</v>
@@ -13602,7 +13599,7 @@
         <v>92</v>
       </c>
       <c r="D258" s="7" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E258" s="7" t="s">
         <v>77</v>
@@ -13617,7 +13614,7 @@
         <v>16</v>
       </c>
       <c r="I258" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J258" s="7" t="s">
         <v>459</v>
@@ -13638,7 +13635,7 @@
         <v>92</v>
       </c>
       <c r="D259" s="7" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E259" s="7" t="s">
         <v>77</v>
@@ -13653,13 +13650,13 @@
         <v>16</v>
       </c>
       <c r="I259" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J259" s="7" t="s">
-        <v>459</v>
+        <v>32</v>
       </c>
       <c r="K259" s="7" t="s">
-        <v>32</v>
+        <v>797</v>
       </c>
       <c r="L259" s="10"/>
     </row>
@@ -13689,13 +13686,13 @@
         <v>16</v>
       </c>
       <c r="I260" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J260" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K260" s="7" t="s">
-        <v>799</v>
+        <v>776</v>
       </c>
       <c r="L260" s="10"/>
     </row>
@@ -13710,7 +13707,7 @@
         <v>92</v>
       </c>
       <c r="D261" s="7" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="E261" s="7" t="s">
         <v>77</v>
@@ -13725,13 +13722,13 @@
         <v>16</v>
       </c>
       <c r="I261" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J261" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K261" s="7" t="s">
-        <v>778</v>
+        <v>800</v>
       </c>
       <c r="L261" s="10"/>
     </row>
@@ -13761,7 +13758,7 @@
         <v>16</v>
       </c>
       <c r="I262" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J262" s="7" t="s">
         <v>32</v>
@@ -13797,7 +13794,7 @@
         <v>16</v>
       </c>
       <c r="I263" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J263" s="7" t="s">
         <v>32</v>
@@ -13833,7 +13830,7 @@
         <v>16</v>
       </c>
       <c r="I264" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J264" s="7" t="s">
         <v>32</v>
@@ -13869,13 +13866,13 @@
         <v>16</v>
       </c>
       <c r="I265" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J265" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K265" s="7" t="s">
-        <v>808</v>
+        <v>788</v>
       </c>
       <c r="L265" s="10"/>
     </row>
@@ -13890,7 +13887,7 @@
         <v>92</v>
       </c>
       <c r="D266" s="7" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="E266" s="7" t="s">
         <v>77</v>
@@ -13905,13 +13902,13 @@
         <v>16</v>
       </c>
       <c r="I266" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J266" s="7" t="s">
-        <v>32</v>
+        <v>459</v>
       </c>
       <c r="K266" s="7" t="s">
-        <v>790</v>
+        <v>32</v>
       </c>
       <c r="L266" s="10"/>
     </row>
@@ -13926,7 +13923,7 @@
         <v>92</v>
       </c>
       <c r="D267" s="7" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E267" s="7" t="s">
         <v>77</v>
@@ -13941,13 +13938,13 @@
         <v>16</v>
       </c>
       <c r="I267" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J267" s="7" t="s">
-        <v>459</v>
+        <v>32</v>
       </c>
       <c r="K267" s="7" t="s">
-        <v>32</v>
+        <v>788</v>
       </c>
       <c r="L267" s="10"/>
     </row>
@@ -13962,7 +13959,7 @@
         <v>92</v>
       </c>
       <c r="D268" s="7" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="E268" s="7" t="s">
         <v>77</v>
@@ -13977,13 +13974,13 @@
         <v>16</v>
       </c>
       <c r="I268" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J268" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K268" s="7" t="s">
-        <v>790</v>
+        <v>811</v>
       </c>
       <c r="L268" s="10"/>
     </row>
@@ -14013,7 +14010,7 @@
         <v>16</v>
       </c>
       <c r="I269" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J269" s="7" t="s">
         <v>32</v>
@@ -14049,7 +14046,7 @@
         <v>16</v>
       </c>
       <c r="I270" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J270" s="7" t="s">
         <v>32</v>
@@ -14067,7 +14064,7 @@
         <v>453</v>
       </c>
       <c r="C271" s="7" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="D271" s="7" t="s">
         <v>816</v>
@@ -14076,7 +14073,7 @@
         <v>77</v>
       </c>
       <c r="F271" s="7" t="s">
-        <v>14</v>
+        <v>464</v>
       </c>
       <c r="G271" s="7" t="s">
         <v>15</v>
@@ -14085,13 +14082,13 @@
         <v>16</v>
       </c>
       <c r="I271" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J271" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K271" s="7" t="s">
-        <v>817</v>
+        <v>32</v>
       </c>
       <c r="L271" s="10"/>
     </row>
@@ -14106,7 +14103,7 @@
         <v>75</v>
       </c>
       <c r="D272" s="7" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="E272" s="7" t="s">
         <v>77</v>
@@ -14121,7 +14118,7 @@
         <v>16</v>
       </c>
       <c r="I272" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J272" s="7" t="s">
         <v>32</v>
@@ -14142,7 +14139,7 @@
         <v>75</v>
       </c>
       <c r="D273" s="7" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="E273" s="7" t="s">
         <v>77</v>
@@ -14157,7 +14154,7 @@
         <v>16</v>
       </c>
       <c r="I273" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J273" s="7" t="s">
         <v>32</v>
@@ -14178,7 +14175,7 @@
         <v>75</v>
       </c>
       <c r="D274" s="7" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="E274" s="7" t="s">
         <v>77</v>
@@ -14193,7 +14190,7 @@
         <v>16</v>
       </c>
       <c r="I274" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J274" s="7" t="s">
         <v>32</v>
@@ -14214,7 +14211,7 @@
         <v>75</v>
       </c>
       <c r="D275" s="7" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E275" s="7" t="s">
         <v>77</v>
@@ -14229,7 +14226,7 @@
         <v>16</v>
       </c>
       <c r="I275" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J275" s="7" t="s">
         <v>32</v>
@@ -14250,7 +14247,7 @@
         <v>75</v>
       </c>
       <c r="D276" s="7" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="E276" s="7" t="s">
         <v>77</v>
@@ -14265,7 +14262,7 @@
         <v>16</v>
       </c>
       <c r="I276" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J276" s="7" t="s">
         <v>32</v>
@@ -14286,7 +14283,7 @@
         <v>75</v>
       </c>
       <c r="D277" s="7" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="E277" s="7" t="s">
         <v>77</v>
@@ -14301,7 +14298,7 @@
         <v>16</v>
       </c>
       <c r="I277" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J277" s="7" t="s">
         <v>32</v>
@@ -14322,7 +14319,7 @@
         <v>75</v>
       </c>
       <c r="D278" s="7" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="E278" s="7" t="s">
         <v>77</v>
@@ -14337,7 +14334,7 @@
         <v>16</v>
       </c>
       <c r="I278" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J278" s="7" t="s">
         <v>32</v>
@@ -14358,7 +14355,7 @@
         <v>75</v>
       </c>
       <c r="D279" s="7" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="E279" s="7" t="s">
         <v>77</v>
@@ -14373,13 +14370,13 @@
         <v>16</v>
       </c>
       <c r="I279" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J279" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K279" s="7" t="s">
-        <v>32</v>
+        <v>825</v>
       </c>
       <c r="L279" s="10"/>
     </row>
@@ -14409,7 +14406,7 @@
         <v>16</v>
       </c>
       <c r="I280" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J280" s="7" t="s">
         <v>32</v>
@@ -14445,7 +14442,7 @@
         <v>16</v>
       </c>
       <c r="I281" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J281" s="7" t="s">
         <v>32</v>
@@ -14481,13 +14478,13 @@
         <v>16</v>
       </c>
       <c r="I282" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J282" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K282" s="7" t="s">
-        <v>831</v>
+        <v>32</v>
       </c>
       <c r="L282" s="10"/>
     </row>
@@ -14502,7 +14499,7 @@
         <v>75</v>
       </c>
       <c r="D283" s="7" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E283" s="7" t="s">
         <v>77</v>
@@ -14517,7 +14514,7 @@
         <v>16</v>
       </c>
       <c r="I283" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J283" s="7" t="s">
         <v>32</v>
@@ -14538,7 +14535,7 @@
         <v>75</v>
       </c>
       <c r="D284" s="7" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E284" s="7" t="s">
         <v>77</v>
@@ -14553,7 +14550,7 @@
         <v>16</v>
       </c>
       <c r="I284" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J284" s="7" t="s">
         <v>32</v>
@@ -14574,7 +14571,7 @@
         <v>75</v>
       </c>
       <c r="D285" s="7" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E285" s="7" t="s">
         <v>77</v>
@@ -14589,13 +14586,13 @@
         <v>16</v>
       </c>
       <c r="I285" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J285" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K285" s="7" t="s">
-        <v>32</v>
+        <v>834</v>
       </c>
       <c r="L285" s="10"/>
     </row>
@@ -14625,13 +14622,13 @@
         <v>16</v>
       </c>
       <c r="I286" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J286" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K286" s="7" t="s">
-        <v>836</v>
+        <v>32</v>
       </c>
       <c r="L286" s="10"/>
     </row>
@@ -14646,7 +14643,7 @@
         <v>75</v>
       </c>
       <c r="D287" s="7" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="E287" s="7" t="s">
         <v>77</v>
@@ -14661,13 +14658,13 @@
         <v>16</v>
       </c>
       <c r="I287" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J287" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K287" s="7" t="s">
-        <v>32</v>
+        <v>837</v>
       </c>
       <c r="L287" s="10"/>
     </row>
@@ -14697,13 +14694,13 @@
         <v>16</v>
       </c>
       <c r="I288" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J288" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K288" s="7" t="s">
-        <v>839</v>
+        <v>32</v>
       </c>
       <c r="L288" s="10"/>
     </row>
@@ -14718,7 +14715,7 @@
         <v>75</v>
       </c>
       <c r="D289" s="7" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="E289" s="7" t="s">
         <v>77</v>
@@ -14733,7 +14730,7 @@
         <v>16</v>
       </c>
       <c r="I289" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J289" s="7" t="s">
         <v>32</v>
@@ -14754,7 +14751,7 @@
         <v>75</v>
       </c>
       <c r="D290" s="7" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="E290" s="7" t="s">
         <v>77</v>
@@ -14769,7 +14766,7 @@
         <v>16</v>
       </c>
       <c r="I290" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J290" s="7" t="s">
         <v>32</v>
@@ -14790,7 +14787,7 @@
         <v>75</v>
       </c>
       <c r="D291" s="7" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="E291" s="7" t="s">
         <v>77</v>
@@ -14805,7 +14802,7 @@
         <v>16</v>
       </c>
       <c r="I291" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J291" s="7" t="s">
         <v>32</v>
@@ -14826,7 +14823,7 @@
         <v>75</v>
       </c>
       <c r="D292" s="7" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="E292" s="7" t="s">
         <v>77</v>
@@ -14841,13 +14838,13 @@
         <v>16</v>
       </c>
       <c r="I292" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J292" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K292" s="7" t="s">
-        <v>32</v>
+        <v>843</v>
       </c>
       <c r="L292" s="10"/>
     </row>
@@ -14877,13 +14874,13 @@
         <v>16</v>
       </c>
       <c r="I293" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J293" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K293" s="7" t="s">
-        <v>845</v>
+        <v>32</v>
       </c>
       <c r="L293" s="10"/>
     </row>
@@ -14898,7 +14895,7 @@
         <v>75</v>
       </c>
       <c r="D294" s="7" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="E294" s="7" t="s">
         <v>77</v>
@@ -14913,7 +14910,7 @@
         <v>16</v>
       </c>
       <c r="I294" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J294" s="7" t="s">
         <v>32</v>
@@ -14934,7 +14931,7 @@
         <v>75</v>
       </c>
       <c r="D295" s="7" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E295" s="7" t="s">
         <v>77</v>
@@ -14949,13 +14946,13 @@
         <v>16</v>
       </c>
       <c r="I295" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J295" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K295" s="7" t="s">
-        <v>32</v>
+        <v>847</v>
       </c>
       <c r="L295" s="10"/>
     </row>
@@ -14985,13 +14982,13 @@
         <v>16</v>
       </c>
       <c r="I296" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J296" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K296" s="7" t="s">
-        <v>849</v>
+        <v>32</v>
       </c>
       <c r="L296" s="10"/>
     </row>
@@ -15006,7 +15003,7 @@
         <v>75</v>
       </c>
       <c r="D297" s="7" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E297" s="7" t="s">
         <v>77</v>
@@ -15021,7 +15018,7 @@
         <v>16</v>
       </c>
       <c r="I297" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J297" s="7" t="s">
         <v>32</v>
@@ -15042,7 +15039,7 @@
         <v>75</v>
       </c>
       <c r="D298" s="7" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="E298" s="7" t="s">
         <v>77</v>
@@ -15057,7 +15054,7 @@
         <v>16</v>
       </c>
       <c r="I298" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J298" s="7" t="s">
         <v>32</v>
@@ -15078,7 +15075,7 @@
         <v>75</v>
       </c>
       <c r="D299" s="7" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="E299" s="7" t="s">
         <v>77</v>
@@ -15093,7 +15090,7 @@
         <v>16</v>
       </c>
       <c r="I299" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J299" s="7" t="s">
         <v>32</v>
@@ -15114,7 +15111,7 @@
         <v>75</v>
       </c>
       <c r="D300" s="7" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="E300" s="7" t="s">
         <v>77</v>
@@ -15129,7 +15126,7 @@
         <v>16</v>
       </c>
       <c r="I300" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J300" s="7" t="s">
         <v>32</v>
@@ -15150,7 +15147,7 @@
         <v>75</v>
       </c>
       <c r="D301" s="7" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="E301" s="7" t="s">
         <v>77</v>
@@ -15165,7 +15162,7 @@
         <v>16</v>
       </c>
       <c r="I301" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J301" s="7" t="s">
         <v>32</v>
@@ -15186,7 +15183,7 @@
         <v>75</v>
       </c>
       <c r="D302" s="7" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="E302" s="7" t="s">
         <v>77</v>
@@ -15201,7 +15198,7 @@
         <v>16</v>
       </c>
       <c r="I302" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J302" s="7" t="s">
         <v>32</v>
@@ -15222,7 +15219,7 @@
         <v>75</v>
       </c>
       <c r="D303" s="7" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="E303" s="7" t="s">
         <v>77</v>
@@ -15237,7 +15234,7 @@
         <v>16</v>
       </c>
       <c r="I303" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J303" s="7" t="s">
         <v>32</v>
@@ -15258,7 +15255,7 @@
         <v>75</v>
       </c>
       <c r="D304" s="7" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="E304" s="7" t="s">
         <v>77</v>
@@ -15273,13 +15270,13 @@
         <v>16</v>
       </c>
       <c r="I304" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J304" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K304" s="7" t="s">
-        <v>32</v>
+        <v>857</v>
       </c>
       <c r="L304" s="10"/>
     </row>
@@ -15309,13 +15306,13 @@
         <v>16</v>
       </c>
       <c r="I305" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J305" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K305" s="7" t="s">
-        <v>859</v>
+        <v>32</v>
       </c>
       <c r="L305" s="10"/>
     </row>
@@ -15330,7 +15327,7 @@
         <v>75</v>
       </c>
       <c r="D306" s="7" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="E306" s="7" t="s">
         <v>77</v>
@@ -15345,7 +15342,7 @@
         <v>16</v>
       </c>
       <c r="I306" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J306" s="7" t="s">
         <v>32</v>
@@ -15366,7 +15363,7 @@
         <v>75</v>
       </c>
       <c r="D307" s="7" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="E307" s="7" t="s">
         <v>77</v>
@@ -15381,13 +15378,13 @@
         <v>16</v>
       </c>
       <c r="I307" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J307" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K307" s="7" t="s">
-        <v>32</v>
+        <v>861</v>
       </c>
       <c r="L307" s="10"/>
     </row>
@@ -15417,13 +15414,13 @@
         <v>16</v>
       </c>
       <c r="I308" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J308" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K308" s="7" t="s">
-        <v>863</v>
+        <v>32</v>
       </c>
       <c r="L308" s="10"/>
     </row>
@@ -15438,7 +15435,7 @@
         <v>75</v>
       </c>
       <c r="D309" s="7" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="E309" s="7" t="s">
         <v>77</v>
@@ -15453,7 +15450,7 @@
         <v>16</v>
       </c>
       <c r="I309" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J309" s="7" t="s">
         <v>32</v>
@@ -15474,7 +15471,7 @@
         <v>75</v>
       </c>
       <c r="D310" s="7" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="E310" s="7" t="s">
         <v>77</v>
@@ -15489,7 +15486,7 @@
         <v>16</v>
       </c>
       <c r="I310" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J310" s="7" t="s">
         <v>32</v>
@@ -15510,7 +15507,7 @@
         <v>75</v>
       </c>
       <c r="D311" s="7" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="E311" s="7" t="s">
         <v>77</v>
@@ -15525,7 +15522,7 @@
         <v>16</v>
       </c>
       <c r="I311" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J311" s="7" t="s">
         <v>32</v>
@@ -15546,7 +15543,7 @@
         <v>75</v>
       </c>
       <c r="D312" s="7" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="E312" s="7" t="s">
         <v>77</v>
@@ -15561,7 +15558,7 @@
         <v>16</v>
       </c>
       <c r="I312" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J312" s="7" t="s">
         <v>32</v>
@@ -15582,7 +15579,7 @@
         <v>75</v>
       </c>
       <c r="D313" s="7" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="E313" s="7" t="s">
         <v>77</v>
@@ -15597,7 +15594,7 @@
         <v>16</v>
       </c>
       <c r="I313" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J313" s="7" t="s">
         <v>32</v>
@@ -15618,7 +15615,7 @@
         <v>75</v>
       </c>
       <c r="D314" s="7" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="E314" s="7" t="s">
         <v>77</v>
@@ -15633,13 +15630,13 @@
         <v>16</v>
       </c>
       <c r="I314" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J314" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K314" s="7" t="s">
-        <v>32</v>
+        <v>869</v>
       </c>
       <c r="L314" s="10"/>
     </row>
@@ -15669,13 +15666,13 @@
         <v>16</v>
       </c>
       <c r="I315" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J315" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K315" s="7" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="L315" s="10"/>
     </row>
@@ -15690,7 +15687,7 @@
         <v>75</v>
       </c>
       <c r="D316" s="7" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="E316" s="7" t="s">
         <v>77</v>
@@ -15705,13 +15702,13 @@
         <v>16</v>
       </c>
       <c r="I316" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J316" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K316" s="7" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="L316" s="10"/>
     </row>
@@ -15726,7 +15723,7 @@
         <v>75</v>
       </c>
       <c r="D317" s="7" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="E317" s="7" t="s">
         <v>77</v>
@@ -15741,13 +15738,13 @@
         <v>16</v>
       </c>
       <c r="I317" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J317" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K317" s="7" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="L317" s="10"/>
     </row>
@@ -15777,13 +15774,13 @@
         <v>16</v>
       </c>
       <c r="I318" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J318" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K318" s="7" t="s">
-        <v>875</v>
+        <v>32</v>
       </c>
       <c r="L318" s="10"/>
     </row>
@@ -15798,28 +15795,28 @@
         <v>75</v>
       </c>
       <c r="D319" s="7" t="s">
+        <v>875</v>
+      </c>
+      <c r="E319" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F319" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G319" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H319" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I319" s="7" t="s">
+        <v>771</v>
+      </c>
+      <c r="J319" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K319" s="7" t="s">
         <v>876</v>
-      </c>
-      <c r="E319" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F319" s="7" t="s">
-        <v>464</v>
-      </c>
-      <c r="G319" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H319" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I319" s="7" t="s">
-        <v>773</v>
-      </c>
-      <c r="J319" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K319" s="7" t="s">
-        <v>32</v>
       </c>
       <c r="L319" s="10"/>
     </row>
@@ -15840,7 +15837,7 @@
         <v>77</v>
       </c>
       <c r="F320" s="7" t="s">
-        <v>14</v>
+        <v>464</v>
       </c>
       <c r="G320" s="7" t="s">
         <v>15</v>
@@ -15849,7 +15846,7 @@
         <v>16</v>
       </c>
       <c r="I320" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J320" s="7" t="s">
         <v>32</v>
@@ -15885,13 +15882,13 @@
         <v>16</v>
       </c>
       <c r="I321" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J321" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K321" s="7" t="s">
-        <v>880</v>
+        <v>32</v>
       </c>
       <c r="L321" s="10"/>
     </row>
@@ -15906,7 +15903,7 @@
         <v>75</v>
       </c>
       <c r="D322" s="7" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="E322" s="7" t="s">
         <v>77</v>
@@ -15921,7 +15918,7 @@
         <v>16</v>
       </c>
       <c r="I322" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J322" s="7" t="s">
         <v>32</v>
@@ -15942,7 +15939,7 @@
         <v>75</v>
       </c>
       <c r="D323" s="7" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="E323" s="7" t="s">
         <v>77</v>
@@ -15957,7 +15954,7 @@
         <v>16</v>
       </c>
       <c r="I323" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J323" s="7" t="s">
         <v>32</v>
@@ -15978,7 +15975,7 @@
         <v>75</v>
       </c>
       <c r="D324" s="7" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="E324" s="7" t="s">
         <v>77</v>
@@ -15993,7 +15990,7 @@
         <v>16</v>
       </c>
       <c r="I324" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J324" s="7" t="s">
         <v>32</v>
@@ -16014,7 +16011,7 @@
         <v>75</v>
       </c>
       <c r="D325" s="7" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="E325" s="7" t="s">
         <v>77</v>
@@ -16029,7 +16026,7 @@
         <v>16</v>
       </c>
       <c r="I325" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J325" s="7" t="s">
         <v>32</v>
@@ -16050,7 +16047,7 @@
         <v>75</v>
       </c>
       <c r="D326" s="7" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="E326" s="7" t="s">
         <v>77</v>
@@ -16065,7 +16062,7 @@
         <v>16</v>
       </c>
       <c r="I326" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J326" s="7" t="s">
         <v>32</v>
@@ -16086,7 +16083,7 @@
         <v>75</v>
       </c>
       <c r="D327" s="7" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="E327" s="7" t="s">
         <v>77</v>
@@ -16101,7 +16098,7 @@
         <v>16</v>
       </c>
       <c r="I327" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J327" s="7" t="s">
         <v>32</v>
@@ -16122,7 +16119,7 @@
         <v>75</v>
       </c>
       <c r="D328" s="7" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E328" s="7" t="s">
         <v>77</v>
@@ -16137,13 +16134,13 @@
         <v>16</v>
       </c>
       <c r="I328" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J328" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K328" s="7" t="s">
-        <v>32</v>
+        <v>887</v>
       </c>
       <c r="L328" s="10"/>
     </row>
@@ -16164,7 +16161,7 @@
         <v>77</v>
       </c>
       <c r="F329" s="7" t="s">
-        <v>464</v>
+        <v>14</v>
       </c>
       <c r="G329" s="7" t="s">
         <v>15</v>
@@ -16173,13 +16170,13 @@
         <v>16</v>
       </c>
       <c r="I329" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J329" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K329" s="7" t="s">
-        <v>889</v>
+        <v>32</v>
       </c>
       <c r="L329" s="10"/>
     </row>
@@ -16194,13 +16191,13 @@
         <v>75</v>
       </c>
       <c r="D330" s="7" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="E330" s="7" t="s">
         <v>77</v>
       </c>
       <c r="F330" s="7" t="s">
-        <v>14</v>
+        <v>464</v>
       </c>
       <c r="G330" s="7" t="s">
         <v>15</v>
@@ -16209,7 +16206,7 @@
         <v>16</v>
       </c>
       <c r="I330" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J330" s="7" t="s">
         <v>32</v>
@@ -16230,7 +16227,7 @@
         <v>75</v>
       </c>
       <c r="D331" s="7" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E331" s="7" t="s">
         <v>77</v>
@@ -16245,13 +16242,13 @@
         <v>16</v>
       </c>
       <c r="I331" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J331" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K331" s="7" t="s">
-        <v>32</v>
+        <v>891</v>
       </c>
       <c r="L331" s="10"/>
     </row>
@@ -16281,13 +16278,13 @@
         <v>16</v>
       </c>
       <c r="I332" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J332" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K332" s="7" t="s">
-        <v>893</v>
+        <v>32</v>
       </c>
       <c r="L332" s="10"/>
     </row>
@@ -16302,7 +16299,7 @@
         <v>75</v>
       </c>
       <c r="D333" s="7" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E333" s="7" t="s">
         <v>77</v>
@@ -16317,13 +16314,13 @@
         <v>16</v>
       </c>
       <c r="I333" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J333" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K333" s="7" t="s">
-        <v>32</v>
+        <v>894</v>
       </c>
       <c r="L333" s="10"/>
     </row>
@@ -16353,13 +16350,13 @@
         <v>16</v>
       </c>
       <c r="I334" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J334" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K334" s="7" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="L334" s="10"/>
     </row>
@@ -16374,7 +16371,7 @@
         <v>75</v>
       </c>
       <c r="D335" s="7" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="E335" s="7" t="s">
         <v>77</v>
@@ -16389,13 +16386,13 @@
         <v>16</v>
       </c>
       <c r="I335" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J335" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K335" s="7" t="s">
-        <v>896</v>
+        <v>32</v>
       </c>
       <c r="L335" s="10"/>
     </row>
@@ -16410,7 +16407,7 @@
         <v>75</v>
       </c>
       <c r="D336" s="7" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="E336" s="7" t="s">
         <v>77</v>
@@ -16425,7 +16422,7 @@
         <v>16</v>
       </c>
       <c r="I336" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J336" s="7" t="s">
         <v>32</v>
@@ -16446,7 +16443,7 @@
         <v>75</v>
       </c>
       <c r="D337" s="7" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="E337" s="7" t="s">
         <v>77</v>
@@ -16461,7 +16458,7 @@
         <v>16</v>
       </c>
       <c r="I337" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J337" s="7" t="s">
         <v>32</v>
@@ -16482,7 +16479,7 @@
         <v>75</v>
       </c>
       <c r="D338" s="7" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="E338" s="7" t="s">
         <v>77</v>
@@ -16497,7 +16494,7 @@
         <v>16</v>
       </c>
       <c r="I338" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J338" s="7" t="s">
         <v>32</v>
@@ -16518,7 +16515,7 @@
         <v>75</v>
       </c>
       <c r="D339" s="7" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="E339" s="7" t="s">
         <v>77</v>
@@ -16533,7 +16530,7 @@
         <v>16</v>
       </c>
       <c r="I339" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J339" s="7" t="s">
         <v>32</v>
@@ -16554,7 +16551,7 @@
         <v>75</v>
       </c>
       <c r="D340" s="7" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="E340" s="7" t="s">
         <v>77</v>
@@ -16569,7 +16566,7 @@
         <v>16</v>
       </c>
       <c r="I340" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J340" s="7" t="s">
         <v>32</v>
@@ -16590,7 +16587,7 @@
         <v>75</v>
       </c>
       <c r="D341" s="7" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="E341" s="7" t="s">
         <v>77</v>
@@ -16605,7 +16602,7 @@
         <v>16</v>
       </c>
       <c r="I341" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J341" s="7" t="s">
         <v>32</v>
@@ -16626,7 +16623,7 @@
         <v>75</v>
       </c>
       <c r="D342" s="7" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="E342" s="7" t="s">
         <v>77</v>
@@ -16641,7 +16638,7 @@
         <v>16</v>
       </c>
       <c r="I342" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J342" s="7" t="s">
         <v>32</v>
@@ -16662,7 +16659,7 @@
         <v>75</v>
       </c>
       <c r="D343" s="7" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="E343" s="7" t="s">
         <v>77</v>
@@ -16677,13 +16674,13 @@
         <v>16</v>
       </c>
       <c r="I343" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J343" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K343" s="7" t="s">
-        <v>32</v>
+        <v>905</v>
       </c>
       <c r="L343" s="10"/>
     </row>
@@ -16713,7 +16710,7 @@
         <v>16</v>
       </c>
       <c r="I344" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J344" s="7" t="s">
         <v>32</v>
@@ -16749,13 +16746,13 @@
         <v>16</v>
       </c>
       <c r="I345" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J345" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K345" s="7" t="s">
-        <v>909</v>
+        <v>32</v>
       </c>
       <c r="L345" s="10"/>
     </row>
@@ -16770,7 +16767,7 @@
         <v>75</v>
       </c>
       <c r="D346" s="7" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E346" s="7" t="s">
         <v>77</v>
@@ -16785,13 +16782,13 @@
         <v>16</v>
       </c>
       <c r="I346" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J346" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K346" s="7" t="s">
-        <v>32</v>
+        <v>910</v>
       </c>
       <c r="L346" s="10"/>
     </row>
@@ -16821,13 +16818,13 @@
         <v>16</v>
       </c>
       <c r="I347" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J347" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K347" s="7" t="s">
-        <v>912</v>
+        <v>32</v>
       </c>
       <c r="L347" s="10"/>
     </row>
@@ -16842,7 +16839,7 @@
         <v>75</v>
       </c>
       <c r="D348" s="7" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="E348" s="7" t="s">
         <v>77</v>
@@ -16857,7 +16854,7 @@
         <v>16</v>
       </c>
       <c r="I348" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J348" s="7" t="s">
         <v>32</v>
@@ -16878,7 +16875,7 @@
         <v>75</v>
       </c>
       <c r="D349" s="7" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E349" s="7" t="s">
         <v>77</v>
@@ -16893,7 +16890,7 @@
         <v>16</v>
       </c>
       <c r="I349" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J349" s="7" t="s">
         <v>32</v>
@@ -16914,7 +16911,7 @@
         <v>75</v>
       </c>
       <c r="D350" s="7" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="E350" s="7" t="s">
         <v>77</v>
@@ -16929,7 +16926,7 @@
         <v>16</v>
       </c>
       <c r="I350" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J350" s="7" t="s">
         <v>32</v>
@@ -16950,7 +16947,7 @@
         <v>75</v>
       </c>
       <c r="D351" s="7" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="E351" s="7" t="s">
         <v>77</v>
@@ -16965,7 +16962,7 @@
         <v>16</v>
       </c>
       <c r="I351" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J351" s="7" t="s">
         <v>32</v>
@@ -16986,7 +16983,7 @@
         <v>75</v>
       </c>
       <c r="D352" s="7" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="E352" s="7" t="s">
         <v>77</v>
@@ -17001,7 +16998,7 @@
         <v>16</v>
       </c>
       <c r="I352" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J352" s="7" t="s">
         <v>32</v>
@@ -17022,7 +17019,7 @@
         <v>75</v>
       </c>
       <c r="D353" s="7" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="E353" s="7" t="s">
         <v>77</v>
@@ -17037,7 +17034,7 @@
         <v>16</v>
       </c>
       <c r="I353" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J353" s="7" t="s">
         <v>32</v>
@@ -17058,7 +17055,7 @@
         <v>75</v>
       </c>
       <c r="D354" s="7" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="E354" s="7" t="s">
         <v>77</v>
@@ -17073,13 +17070,13 @@
         <v>16</v>
       </c>
       <c r="I354" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J354" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K354" s="7" t="s">
-        <v>32</v>
+        <v>919</v>
       </c>
       <c r="L354" s="10"/>
     </row>
@@ -17109,13 +17106,13 @@
         <v>16</v>
       </c>
       <c r="I355" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J355" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K355" s="7" t="s">
-        <v>921</v>
+        <v>32</v>
       </c>
       <c r="L355" s="10"/>
     </row>
@@ -17130,7 +17127,7 @@
         <v>75</v>
       </c>
       <c r="D356" s="7" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="E356" s="7" t="s">
         <v>77</v>
@@ -17145,13 +17142,13 @@
         <v>16</v>
       </c>
       <c r="I356" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J356" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K356" s="7" t="s">
-        <v>32</v>
+        <v>922</v>
       </c>
       <c r="L356" s="10"/>
     </row>
@@ -17181,7 +17178,7 @@
         <v>16</v>
       </c>
       <c r="I357" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J357" s="7" t="s">
         <v>32</v>
@@ -17217,13 +17214,13 @@
         <v>16</v>
       </c>
       <c r="I358" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J358" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K358" s="7" t="s">
-        <v>926</v>
+        <v>32</v>
       </c>
       <c r="L358" s="10"/>
     </row>
@@ -17238,7 +17235,7 @@
         <v>75</v>
       </c>
       <c r="D359" s="7" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="E359" s="7" t="s">
         <v>77</v>
@@ -17253,7 +17250,7 @@
         <v>16</v>
       </c>
       <c r="I359" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J359" s="7" t="s">
         <v>32</v>
@@ -17274,7 +17271,7 @@
         <v>75</v>
       </c>
       <c r="D360" s="7" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="E360" s="7" t="s">
         <v>77</v>
@@ -17289,13 +17286,13 @@
         <v>16</v>
       </c>
       <c r="I360" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J360" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K360" s="7" t="s">
-        <v>32</v>
+        <v>928</v>
       </c>
       <c r="L360" s="10"/>
     </row>
@@ -17325,13 +17322,13 @@
         <v>16</v>
       </c>
       <c r="I361" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J361" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K361" s="7" t="s">
-        <v>930</v>
+        <v>32</v>
       </c>
       <c r="L361" s="10"/>
     </row>
@@ -17346,7 +17343,7 @@
         <v>75</v>
       </c>
       <c r="D362" s="7" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E362" s="7" t="s">
         <v>77</v>
@@ -17361,7 +17358,7 @@
         <v>16</v>
       </c>
       <c r="I362" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J362" s="7" t="s">
         <v>32</v>
@@ -17382,7 +17379,7 @@
         <v>75</v>
       </c>
       <c r="D363" s="7" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="E363" s="7" t="s">
         <v>77</v>
@@ -17397,7 +17394,7 @@
         <v>16</v>
       </c>
       <c r="I363" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J363" s="7" t="s">
         <v>32</v>
@@ -17418,7 +17415,7 @@
         <v>75</v>
       </c>
       <c r="D364" s="7" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="E364" s="7" t="s">
         <v>77</v>
@@ -17433,7 +17430,7 @@
         <v>16</v>
       </c>
       <c r="I364" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J364" s="7" t="s">
         <v>32</v>
@@ -17454,7 +17451,7 @@
         <v>75</v>
       </c>
       <c r="D365" s="7" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="E365" s="7" t="s">
         <v>77</v>
@@ -17469,7 +17466,7 @@
         <v>16</v>
       </c>
       <c r="I365" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J365" s="7" t="s">
         <v>32</v>
@@ -17490,7 +17487,7 @@
         <v>75</v>
       </c>
       <c r="D366" s="7" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="E366" s="7" t="s">
         <v>77</v>
@@ -17505,7 +17502,7 @@
         <v>16</v>
       </c>
       <c r="I366" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J366" s="7" t="s">
         <v>32</v>
@@ -17523,31 +17520,31 @@
         <v>453</v>
       </c>
       <c r="C367" s="7" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="D367" s="7" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="E367" s="7" t="s">
         <v>77</v>
       </c>
       <c r="F367" s="7" t="s">
-        <v>464</v>
+        <v>39</v>
       </c>
       <c r="G367" s="7" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H367" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I367" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J367" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K367" s="7" t="s">
-        <v>32</v>
+        <v>456</v>
       </c>
       <c r="L367" s="10"/>
     </row>
@@ -17562,7 +17559,7 @@
         <v>114</v>
       </c>
       <c r="D368" s="7" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="E368" s="7" t="s">
         <v>77</v>
@@ -17577,13 +17574,13 @@
         <v>16</v>
       </c>
       <c r="I368" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J368" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K368" s="7" t="s">
-        <v>456</v>
+        <v>937</v>
       </c>
       <c r="L368" s="10"/>
     </row>
@@ -17613,7 +17610,7 @@
         <v>16</v>
       </c>
       <c r="I369" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J369" s="7" t="s">
         <v>32</v>
@@ -17649,7 +17646,7 @@
         <v>16</v>
       </c>
       <c r="I370" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J370" s="7" t="s">
         <v>32</v>
@@ -17685,13 +17682,13 @@
         <v>16</v>
       </c>
       <c r="I371" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J371" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K371" s="7" t="s">
-        <v>943</v>
+        <v>32</v>
       </c>
       <c r="L371" s="10"/>
     </row>
@@ -17706,7 +17703,7 @@
         <v>114</v>
       </c>
       <c r="D372" s="7" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="E372" s="7" t="s">
         <v>77</v>
@@ -17721,13 +17718,13 @@
         <v>16</v>
       </c>
       <c r="I372" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J372" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K372" s="7" t="s">
-        <v>32</v>
+        <v>944</v>
       </c>
       <c r="L372" s="10"/>
     </row>
@@ -17757,7 +17754,7 @@
         <v>16</v>
       </c>
       <c r="I373" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J373" s="7" t="s">
         <v>32</v>
@@ -17793,7 +17790,7 @@
         <v>16</v>
       </c>
       <c r="I374" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J374" s="7" t="s">
         <v>32</v>
@@ -17829,7 +17826,7 @@
         <v>16</v>
       </c>
       <c r="I375" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J375" s="7" t="s">
         <v>32</v>
@@ -17865,7 +17862,7 @@
         <v>16</v>
       </c>
       <c r="I376" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J376" s="7" t="s">
         <v>32</v>
@@ -17901,7 +17898,7 @@
         <v>16</v>
       </c>
       <c r="I377" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J377" s="7" t="s">
         <v>32</v>
@@ -17937,7 +17934,7 @@
         <v>16</v>
       </c>
       <c r="I378" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J378" s="7" t="s">
         <v>32</v>
@@ -17973,7 +17970,7 @@
         <v>16</v>
       </c>
       <c r="I379" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J379" s="7" t="s">
         <v>32</v>
@@ -18009,7 +18006,7 @@
         <v>16</v>
       </c>
       <c r="I380" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J380" s="7" t="s">
         <v>32</v>
@@ -18045,13 +18042,13 @@
         <v>16</v>
       </c>
       <c r="I381" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J381" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K381" s="7" t="s">
-        <v>962</v>
+        <v>32</v>
       </c>
       <c r="L381" s="10"/>
     </row>
@@ -18066,7 +18063,7 @@
         <v>114</v>
       </c>
       <c r="D382" s="7" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="E382" s="7" t="s">
         <v>77</v>
@@ -18081,7 +18078,7 @@
         <v>16</v>
       </c>
       <c r="I382" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J382" s="7" t="s">
         <v>32</v>
@@ -18102,7 +18099,7 @@
         <v>114</v>
       </c>
       <c r="D383" s="7" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="E383" s="7" t="s">
         <v>77</v>
@@ -18117,7 +18114,7 @@
         <v>16</v>
       </c>
       <c r="I383" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J383" s="7" t="s">
         <v>32</v>
@@ -18138,7 +18135,7 @@
         <v>114</v>
       </c>
       <c r="D384" s="7" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E384" s="7" t="s">
         <v>77</v>
@@ -18153,13 +18150,13 @@
         <v>16</v>
       </c>
       <c r="I384" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J384" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K384" s="7" t="s">
-        <v>32</v>
+        <v>965</v>
       </c>
       <c r="L384" s="10"/>
     </row>
@@ -18189,13 +18186,13 @@
         <v>16</v>
       </c>
       <c r="I385" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J385" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K385" s="7" t="s">
-        <v>967</v>
+        <v>32</v>
       </c>
       <c r="L385" s="10"/>
     </row>
@@ -18210,7 +18207,7 @@
         <v>114</v>
       </c>
       <c r="D386" s="7" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="E386" s="7" t="s">
         <v>77</v>
@@ -18225,13 +18222,13 @@
         <v>16</v>
       </c>
       <c r="I386" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J386" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K386" s="7" t="s">
-        <v>32</v>
+        <v>968</v>
       </c>
       <c r="L386" s="10"/>
     </row>
@@ -18261,7 +18258,7 @@
         <v>16</v>
       </c>
       <c r="I387" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J387" s="7" t="s">
         <v>32</v>
@@ -18297,7 +18294,7 @@
         <v>16</v>
       </c>
       <c r="I388" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J388" s="7" t="s">
         <v>32</v>
@@ -18333,7 +18330,7 @@
         <v>16</v>
       </c>
       <c r="I389" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J389" s="7" t="s">
         <v>32</v>
@@ -18351,7 +18348,7 @@
         <v>453</v>
       </c>
       <c r="C390" s="7" t="s">
-        <v>114</v>
+        <v>11</v>
       </c>
       <c r="D390" s="7" t="s">
         <v>975</v>
@@ -18360,16 +18357,16 @@
         <v>77</v>
       </c>
       <c r="F390" s="7" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="G390" s="7" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H390" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I390" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J390" s="7" t="s">
         <v>32</v>
@@ -18405,7 +18402,7 @@
         <v>16</v>
       </c>
       <c r="I391" s="7" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="J391" s="7" t="s">
         <v>32</v>
@@ -18420,16 +18417,16 @@
         <v>391</v>
       </c>
       <c r="B392" s="7" t="s">
-        <v>453</v>
+        <v>979</v>
       </c>
       <c r="C392" s="7" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D392" s="7" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="E392" s="7" t="s">
-        <v>77</v>
+        <v>981</v>
       </c>
       <c r="F392" s="7" t="s">
         <v>14</v>
@@ -18441,13 +18438,13 @@
         <v>16</v>
       </c>
       <c r="I392" s="7" t="s">
-        <v>773</v>
+        <v>982</v>
       </c>
       <c r="J392" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K392" s="7" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="L392" s="10"/>
     </row>
@@ -18456,16 +18453,16 @@
         <v>392</v>
       </c>
       <c r="B393" s="7" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="C393" s="7" t="s">
         <v>26</v>
       </c>
       <c r="D393" s="7" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="E393" s="7" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="F393" s="7" t="s">
         <v>14</v>
@@ -18477,13 +18474,13 @@
         <v>16</v>
       </c>
       <c r="I393" s="7" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="J393" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K393" s="7" t="s">
-        <v>985</v>
+        <v>32</v>
       </c>
       <c r="L393" s="10"/>
     </row>
@@ -18492,16 +18489,16 @@
         <v>393</v>
       </c>
       <c r="B394" s="7" t="s">
-        <v>981</v>
+        <v>148</v>
       </c>
       <c r="C394" s="7" t="s">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="D394" s="7" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E394" s="7" t="s">
-        <v>983</v>
+        <v>150</v>
       </c>
       <c r="F394" s="7" t="s">
         <v>14</v>
@@ -18513,7 +18510,7 @@
         <v>16</v>
       </c>
       <c r="I394" s="7" t="s">
-        <v>984</v>
+        <v>151</v>
       </c>
       <c r="J394" s="7" t="s">
         <v>32</v>
@@ -18534,7 +18531,7 @@
         <v>138</v>
       </c>
       <c r="D395" s="7" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E395" s="7" t="s">
         <v>150</v>
@@ -18555,7 +18552,7 @@
         <v>32</v>
       </c>
       <c r="K395" s="7" t="s">
-        <v>32</v>
+        <v>987</v>
       </c>
       <c r="L395" s="10"/>
     </row>
@@ -18567,7 +18564,7 @@
         <v>148</v>
       </c>
       <c r="C396" s="7" t="s">
-        <v>138</v>
+        <v>26</v>
       </c>
       <c r="D396" s="7" t="s">
         <v>988</v>
@@ -18663,7 +18660,7 @@
         <v>32</v>
       </c>
       <c r="K398" s="7" t="s">
-        <v>993</v>
+        <v>32</v>
       </c>
       <c r="L398" s="10"/>
     </row>
@@ -18678,7 +18675,7 @@
         <v>26</v>
       </c>
       <c r="D399" s="7" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="E399" s="7" t="s">
         <v>150</v>
@@ -18699,7 +18696,7 @@
         <v>32</v>
       </c>
       <c r="K399" s="7" t="s">
-        <v>32</v>
+        <v>994</v>
       </c>
       <c r="L399" s="10"/>
     </row>
@@ -18927,7 +18924,7 @@
         <v>148</v>
       </c>
       <c r="C406" s="7" t="s">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="D406" s="7" t="s">
         <v>1007</v>
@@ -18963,7 +18960,7 @@
         <v>148</v>
       </c>
       <c r="C407" s="7" t="s">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="D407" s="7" t="s">
         <v>1009</v>
@@ -19059,7 +19056,7 @@
         <v>32</v>
       </c>
       <c r="K409" s="7" t="s">
-        <v>1014</v>
+        <v>996</v>
       </c>
       <c r="L409" s="10"/>
     </row>
@@ -19074,7 +19071,7 @@
         <v>75</v>
       </c>
       <c r="D410" s="7" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="E410" s="7" t="s">
         <v>150</v>
@@ -19095,7 +19092,7 @@
         <v>32</v>
       </c>
       <c r="K410" s="7" t="s">
-        <v>998</v>
+        <v>32</v>
       </c>
       <c r="L410" s="10"/>
     </row>
@@ -19110,7 +19107,7 @@
         <v>75</v>
       </c>
       <c r="D411" s="7" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="E411" s="7" t="s">
         <v>150</v>
@@ -19146,7 +19143,7 @@
         <v>75</v>
       </c>
       <c r="D412" s="7" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E412" s="7" t="s">
         <v>150</v>
@@ -19182,7 +19179,7 @@
         <v>75</v>
       </c>
       <c r="D413" s="7" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="E413" s="7" t="s">
         <v>150</v>
@@ -19203,7 +19200,7 @@
         <v>32</v>
       </c>
       <c r="K413" s="7" t="s">
-        <v>32</v>
+        <v>1018</v>
       </c>
       <c r="L413" s="10"/>
     </row>
@@ -19275,7 +19272,7 @@
         <v>32</v>
       </c>
       <c r="K415" s="7" t="s">
-        <v>1022</v>
+        <v>32</v>
       </c>
       <c r="L415" s="10"/>
     </row>
@@ -19290,7 +19287,7 @@
         <v>75</v>
       </c>
       <c r="D416" s="7" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="E416" s="7" t="s">
         <v>150</v>
@@ -19326,7 +19323,7 @@
         <v>75</v>
       </c>
       <c r="D417" s="7" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E417" s="7" t="s">
         <v>150</v>
@@ -19359,10 +19356,10 @@
         <v>148</v>
       </c>
       <c r="C418" s="7" t="s">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="D418" s="7" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="E418" s="7" t="s">
         <v>150</v>
@@ -19383,7 +19380,7 @@
         <v>32</v>
       </c>
       <c r="K418" s="7" t="s">
-        <v>32</v>
+        <v>1025</v>
       </c>
       <c r="L418" s="10"/>
     </row>
@@ -19428,34 +19425,34 @@
         <v>419</v>
       </c>
       <c r="B420" s="7" t="s">
-        <v>148</v>
+        <v>1091</v>
       </c>
       <c r="C420" s="7" t="s">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="D420" s="7" t="s">
         <v>1028</v>
       </c>
       <c r="E420" s="7" t="s">
-        <v>150</v>
+        <v>644</v>
       </c>
       <c r="F420" s="7" t="s">
-        <v>14</v>
+        <v>1029</v>
       </c>
       <c r="G420" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H420" s="7" t="s">
-        <v>16</v>
+        <v>1030</v>
       </c>
       <c r="I420" s="7" t="s">
-        <v>151</v>
+        <v>102</v>
       </c>
       <c r="J420" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K420" s="7" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="L420" s="10"/>
     </row>
@@ -19464,25 +19461,25 @@
         <v>420</v>
       </c>
       <c r="B421" s="7" t="s">
-        <v>1093</v>
+        <v>1032</v>
       </c>
       <c r="C421" s="7" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="D421" s="7" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="E421" s="7" t="s">
-        <v>646</v>
+        <v>77</v>
       </c>
       <c r="F421" s="7" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="G421" s="7" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H421" s="7" t="s">
-        <v>1032</v>
+        <v>16</v>
       </c>
       <c r="I421" s="7" t="s">
         <v>102</v>
@@ -19491,7 +19488,7 @@
         <v>32</v>
       </c>
       <c r="K421" s="7" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="L421" s="10"/>
     </row>
@@ -19500,19 +19497,19 @@
         <v>421</v>
       </c>
       <c r="B422" s="7" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C422" s="7" t="s">
-        <v>114</v>
+        <v>26</v>
       </c>
       <c r="D422" s="7" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="E422" s="7" t="s">
         <v>77</v>
       </c>
       <c r="F422" s="7" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="G422" s="7" t="s">
         <v>39</v>
@@ -19527,7 +19524,7 @@
         <v>32</v>
       </c>
       <c r="K422" s="7" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="L422" s="10"/>
     </row>
@@ -19536,19 +19533,19 @@
         <v>422</v>
       </c>
       <c r="B423" s="7" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C423" s="7" t="s">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="D423" s="7" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="E423" s="7" t="s">
         <v>77</v>
       </c>
       <c r="F423" s="7" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="G423" s="7" t="s">
         <v>39</v>
@@ -19563,7 +19560,7 @@
         <v>32</v>
       </c>
       <c r="K423" s="7" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="L423" s="10"/>
     </row>
@@ -19572,22 +19569,22 @@
         <v>423</v>
       </c>
       <c r="B424" s="7" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C424" s="7" t="s">
-        <v>138</v>
+        <v>26</v>
       </c>
       <c r="D424" s="7" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="E424" s="7" t="s">
         <v>77</v>
       </c>
       <c r="F424" s="7" t="s">
-        <v>1042</v>
+        <v>56</v>
       </c>
       <c r="G424" s="7" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H424" s="7" t="s">
         <v>16</v>
@@ -19599,7 +19596,7 @@
         <v>32</v>
       </c>
       <c r="K424" s="7" t="s">
-        <v>1043</v>
+        <v>32</v>
       </c>
       <c r="L424" s="10"/>
     </row>
@@ -19608,19 +19605,19 @@
         <v>424</v>
       </c>
       <c r="B425" s="7" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="C425" s="7" t="s">
-        <v>26</v>
+        <v>92</v>
       </c>
       <c r="D425" s="7" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E425" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="F425" s="7" t="s">
         <v>1044</v>
-      </c>
-      <c r="E425" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="F425" s="7" t="s">
-        <v>56</v>
       </c>
       <c r="G425" s="7" t="s">
         <v>15</v>
@@ -19632,7 +19629,7 @@
         <v>102</v>
       </c>
       <c r="J425" s="7" t="s">
-        <v>32</v>
+        <v>1045</v>
       </c>
       <c r="K425" s="7" t="s">
         <v>32</v>
@@ -19644,19 +19641,19 @@
         <v>425</v>
       </c>
       <c r="B426" s="7" t="s">
-        <v>1034</v>
+        <v>504</v>
       </c>
       <c r="C426" s="7" t="s">
         <v>92</v>
       </c>
       <c r="D426" s="7" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="E426" s="7" t="s">
-        <v>77</v>
+        <v>478</v>
       </c>
       <c r="F426" s="7" t="s">
-        <v>1046</v>
+        <v>78</v>
       </c>
       <c r="G426" s="7" t="s">
         <v>15</v>
@@ -19665,7 +19662,7 @@
         <v>16</v>
       </c>
       <c r="I426" s="7" t="s">
-        <v>102</v>
+        <v>506</v>
       </c>
       <c r="J426" s="7" t="s">
         <v>1047</v>
@@ -19683,7 +19680,7 @@
         <v>504</v>
       </c>
       <c r="C427" s="7" t="s">
-        <v>92</v>
+        <v>26</v>
       </c>
       <c r="D427" s="7" t="s">
         <v>1048</v>
@@ -19692,22 +19689,22 @@
         <v>478</v>
       </c>
       <c r="F427" s="7" t="s">
-        <v>78</v>
+        <v>1049</v>
       </c>
       <c r="G427" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H427" s="7" t="s">
-        <v>16</v>
+        <v>1050</v>
       </c>
       <c r="I427" s="7" t="s">
         <v>506</v>
       </c>
       <c r="J427" s="7" t="s">
-        <v>1049</v>
+        <v>32</v>
       </c>
       <c r="K427" s="7" t="s">
-        <v>32</v>
+        <v>1051</v>
       </c>
       <c r="L427" s="10"/>
     </row>
@@ -19716,34 +19713,34 @@
         <v>427</v>
       </c>
       <c r="B428" s="7" t="s">
-        <v>504</v>
+        <v>1052</v>
       </c>
       <c r="C428" s="7" t="s">
-        <v>26</v>
+        <v>92</v>
       </c>
       <c r="D428" s="7" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="E428" s="7" t="s">
-        <v>478</v>
+        <v>1054</v>
       </c>
       <c r="F428" s="7" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="G428" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H428" s="7" t="s">
-        <v>1052</v>
+        <v>16</v>
       </c>
       <c r="I428" s="7" t="s">
-        <v>506</v>
+        <v>1056</v>
       </c>
       <c r="J428" s="7" t="s">
-        <v>32</v>
+        <v>1057</v>
       </c>
       <c r="K428" s="7" t="s">
-        <v>1053</v>
+        <v>32</v>
       </c>
       <c r="L428" s="10"/>
     </row>
@@ -19752,34 +19749,34 @@
         <v>428</v>
       </c>
       <c r="B429" s="7" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C429" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D429" s="7" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E429" s="7" t="s">
         <v>1054</v>
       </c>
-      <c r="C429" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D429" s="7" t="s">
-        <v>1055</v>
-      </c>
-      <c r="E429" s="7" t="s">
+      <c r="F429" s="7" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G429" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H429" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I429" s="7" t="s">
         <v>1056</v>
       </c>
-      <c r="F429" s="7" t="s">
-        <v>1057</v>
-      </c>
-      <c r="G429" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H429" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I429" s="7" t="s">
-        <v>1058</v>
-      </c>
       <c r="J429" s="7" t="s">
-        <v>1059</v>
+        <v>32</v>
       </c>
       <c r="K429" s="7" t="s">
-        <v>32</v>
+        <v>1060</v>
       </c>
       <c r="L429" s="10"/>
     </row>
@@ -19788,34 +19785,34 @@
         <v>429</v>
       </c>
       <c r="B430" s="7" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C430" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D430" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E430" s="7" t="s">
         <v>1054</v>
       </c>
-      <c r="C430" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="D430" s="7" t="s">
-        <v>1060</v>
-      </c>
-      <c r="E430" s="7" t="s">
+      <c r="F430" s="7" t="s">
+        <v>1055</v>
+      </c>
+      <c r="G430" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H430" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I430" s="7" t="s">
         <v>1056</v>
       </c>
-      <c r="F430" s="7" t="s">
-        <v>1061</v>
-      </c>
-      <c r="G430" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="H430" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I430" s="7" t="s">
-        <v>1058</v>
-      </c>
       <c r="J430" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K430" s="7" t="s">
-        <v>1062</v>
+        <v>32</v>
       </c>
       <c r="L430" s="10"/>
     </row>
@@ -19824,28 +19821,28 @@
         <v>430</v>
       </c>
       <c r="B431" s="7" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C431" s="7" t="s">
-        <v>75</v>
+        <v>138</v>
       </c>
       <c r="D431" s="7" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E431" s="7" t="s">
         <v>1063</v>
       </c>
-      <c r="E431" s="7" t="s">
+      <c r="F431" s="7" t="s">
+        <v>1055</v>
+      </c>
+      <c r="G431" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H431" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I431" s="7" t="s">
         <v>1056</v>
-      </c>
-      <c r="F431" s="7" t="s">
-        <v>1057</v>
-      </c>
-      <c r="G431" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H431" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I431" s="7" t="s">
-        <v>1058</v>
       </c>
       <c r="J431" s="7" t="s">
         <v>32</v>
@@ -19860,7 +19857,7 @@
         <v>431</v>
       </c>
       <c r="B432" s="7" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C432" s="7" t="s">
         <v>138</v>
@@ -19872,22 +19869,22 @@
         <v>1065</v>
       </c>
       <c r="F432" s="7" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="G432" s="7" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="H432" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I432" s="7" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="J432" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K432" s="7" t="s">
-        <v>32</v>
+        <v>1066</v>
       </c>
       <c r="L432" s="10"/>
     </row>
@@ -19896,34 +19893,34 @@
         <v>432</v>
       </c>
       <c r="B433" s="7" t="s">
-        <v>1054</v>
+        <v>10</v>
       </c>
       <c r="C433" s="7" t="s">
-        <v>138</v>
+        <v>11</v>
       </c>
       <c r="D433" s="7" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="E433" s="7" t="s">
-        <v>1067</v>
+        <v>55</v>
       </c>
       <c r="F433" s="7" t="s">
-        <v>1061</v>
+        <v>1068</v>
       </c>
       <c r="G433" s="7" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="H433" s="7" t="s">
         <v>16</v>
       </c>
       <c r="I433" s="7" t="s">
-        <v>1058</v>
+        <v>30</v>
       </c>
       <c r="J433" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K433" s="7" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="L433" s="10"/>
     </row>
@@ -19935,16 +19932,16 @@
         <v>10</v>
       </c>
       <c r="C434" s="7" t="s">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="D434" s="7" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="E434" s="7" t="s">
         <v>55</v>
       </c>
       <c r="F434" s="7" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G434" s="7" t="s">
         <v>15</v>
@@ -19980,7 +19977,7 @@
         <v>55</v>
       </c>
       <c r="F435" s="7" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G435" s="7" t="s">
         <v>15</v>
@@ -20007,16 +20004,16 @@
         <v>10</v>
       </c>
       <c r="C436" s="7" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="D436" s="7" t="s">
         <v>1074</v>
       </c>
       <c r="E436" s="7" t="s">
-        <v>55</v>
+        <v>617</v>
       </c>
       <c r="F436" s="7" t="s">
-        <v>1070</v>
+        <v>172</v>
       </c>
       <c r="G436" s="7" t="s">
         <v>15</v>
@@ -20031,7 +20028,7 @@
         <v>32</v>
       </c>
       <c r="K436" s="7" t="s">
-        <v>1075</v>
+        <v>32</v>
       </c>
       <c r="L436" s="10"/>
     </row>
@@ -20040,19 +20037,19 @@
         <v>436</v>
       </c>
       <c r="B437" s="7" t="s">
-        <v>10</v>
+        <v>525</v>
       </c>
       <c r="C437" s="7" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="D437" s="7" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E437" s="7" t="s">
         <v>1076</v>
       </c>
-      <c r="E437" s="7" t="s">
-        <v>619</v>
-      </c>
       <c r="F437" s="7" t="s">
-        <v>172</v>
+        <v>14</v>
       </c>
       <c r="G437" s="7" t="s">
         <v>15</v>
@@ -20061,13 +20058,13 @@
         <v>16</v>
       </c>
       <c r="I437" s="7" t="s">
-        <v>30</v>
+        <v>1077</v>
       </c>
       <c r="J437" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K437" s="7" t="s">
-        <v>32</v>
+        <v>1078</v>
       </c>
       <c r="L437" s="10"/>
     </row>
@@ -20082,10 +20079,10 @@
         <v>75</v>
       </c>
       <c r="D438" s="7" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="E438" s="7" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="F438" s="7" t="s">
         <v>14</v>
@@ -20097,13 +20094,13 @@
         <v>16</v>
       </c>
       <c r="I438" s="7" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="J438" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K438" s="7" t="s">
-        <v>1080</v>
+        <v>32</v>
       </c>
       <c r="L438" s="10"/>
     </row>
@@ -20112,34 +20109,34 @@
         <v>438</v>
       </c>
       <c r="B439" s="7" t="s">
-        <v>525</v>
+        <v>1080</v>
       </c>
       <c r="C439" s="7" t="s">
-        <v>75</v>
+        <v>231</v>
       </c>
       <c r="D439" s="7" t="s">
         <v>1081</v>
       </c>
       <c r="E439" s="7" t="s">
-        <v>1078</v>
+        <v>478</v>
       </c>
       <c r="F439" s="7" t="s">
-        <v>14</v>
+        <v>1082</v>
       </c>
       <c r="G439" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H439" s="7" t="s">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="I439" s="7" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="J439" s="7" t="s">
         <v>32</v>
       </c>
       <c r="K439" s="7" t="s">
-        <v>32</v>
+        <v>1084</v>
       </c>
       <c r="L439" s="10"/>
     </row>
@@ -20148,19 +20145,19 @@
         <v>439</v>
       </c>
       <c r="B440" s="7" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C440" s="7" t="s">
         <v>231</v>
       </c>
       <c r="D440" s="7" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="E440" s="7" t="s">
         <v>478</v>
       </c>
       <c r="F440" s="7" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="G440" s="7" t="s">
         <v>15</v>
@@ -20169,12 +20166,12 @@
         <v>101</v>
       </c>
       <c r="I440" s="7" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J440" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="K440" s="7" t="s">
+      <c r="K440" s="27" t="s">
         <v>1086</v>
       </c>
       <c r="L440" s="10"/>
@@ -20183,82 +20180,46 @@
       <c r="A441" s="11">
         <v>440</v>
       </c>
-      <c r="B441" s="7" t="s">
+      <c r="B441" s="21" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C441" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="D441" s="21" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E441" s="21" t="s">
+        <v>478</v>
+      </c>
+      <c r="F441" s="21" t="s">
         <v>1082</v>
       </c>
-      <c r="C441" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="D441" s="7" t="s">
-        <v>1087</v>
-      </c>
-      <c r="E441" s="7" t="s">
-        <v>478</v>
-      </c>
-      <c r="F441" s="7" t="s">
-        <v>1084</v>
-      </c>
-      <c r="G441" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H441" s="7" t="s">
+      <c r="G441" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H441" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="I441" s="7" t="s">
-        <v>1085</v>
-      </c>
-      <c r="J441" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K441" s="27" t="s">
+      <c r="I441" s="21" t="s">
+        <v>1083</v>
+      </c>
+      <c r="J441" s="22" t="s">
         <v>1088</v>
       </c>
-      <c r="L441" s="10"/>
-    </row>
-    <row r="442" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A442" s="11">
-        <v>441</v>
-      </c>
-      <c r="B442" s="21" t="s">
-        <v>1082</v>
-      </c>
-      <c r="C442" s="21" t="s">
-        <v>231</v>
-      </c>
-      <c r="D442" s="21" t="s">
+      <c r="K441" s="28" t="s">
         <v>1089</v>
       </c>
-      <c r="E442" s="21" t="s">
-        <v>478</v>
-      </c>
-      <c r="F442" s="21" t="s">
-        <v>1084</v>
-      </c>
-      <c r="G442" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="H442" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="I442" s="21" t="s">
-        <v>1085</v>
-      </c>
-      <c r="J442" s="22" t="s">
+      <c r="L441" s="29" t="s">
         <v>1090</v>
-      </c>
-      <c r="K442" s="28" t="s">
-        <v>1091</v>
-      </c>
-      <c r="L442" s="29" t="s">
-        <v>1092</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="duplicateValues" dxfId="19" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="J7" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -20268,8 +20229,8 @@
     <hyperlink ref="J23" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
     <hyperlink ref="J29" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
     <hyperlink ref="J30" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="J199" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="J442" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="J198" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="J441" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
